--- a/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
+++ b/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Algoritms" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="845">
   <si>
     <t xml:space="preserve">Data structures are the fundamental building blocks of computer programming.</t>
   </si>
@@ -35,16 +35,16 @@
     <t xml:space="preserve">ˈdeɪtə ˈstrʌkʧərz ɑr ðə ˌfʌndəˈmɛntəl ˈbɪldɪŋ blɑks ʌv kəmˈpjutər ˈproʊˌɡræmɪŋ.</t>
   </si>
   <si>
+    <t xml:space="preserve">They define how data is organized, stored, and manipulated within a program.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definen cómo se organizan, almacenan y manipulan los datos dentro de un programa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ðeɪ dɪˈfaɪn haʊ ˈdeɪtə ɪz ˈɔrɡəˌnaɪzd, stɔrd, ænd məˈnɪpjəˌleɪtɪd wɪˈðɪn ə ˈproʊˌɡræm.</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXAMPLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They define how data is organized, stored, and manipulated within a program.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definen cómo se organizan, almacenan y manipulan los datos dentro de un programa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðeɪ dɪˈfaɪn haʊ ˈdeɪtə ɪz ˈɔrɡəˌnaɪzd, stɔrd, ænd məˈnɪpjəˌleɪtɪd wɪˈðɪn ə ˈproʊˌɡræm.</t>
   </si>
   <si>
     <t xml:space="preserve">Understanding data structures is very important for developing efficient and effective algorithms.</t>
@@ -2665,9 +2665,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4686840</xdr:colOff>
+      <xdr:colOff>4686480</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2383920</xdr:rowOff>
+      <xdr:rowOff>2383560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2681,7 +2681,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="1788120"/>
-          <a:ext cx="4686840" cy="2383920"/>
+          <a:ext cx="4686480" cy="2383560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2703,9 +2703,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843440</xdr:colOff>
+      <xdr:colOff>4843080</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>2343600</xdr:rowOff>
+      <xdr:rowOff>2343240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2719,7 +2719,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="12969720"/>
-          <a:ext cx="4843440" cy="2343600"/>
+          <a:ext cx="4843080" cy="2343240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2741,9 +2741,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4825440</xdr:colOff>
+      <xdr:colOff>4825080</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>2333160</xdr:rowOff>
+      <xdr:rowOff>2332800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2757,7 +2757,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="16629840"/>
-          <a:ext cx="4825440" cy="2333160"/>
+          <a:ext cx="4825080" cy="2332800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2779,9 +2779,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4782600</xdr:colOff>
+      <xdr:colOff>4782240</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>2314080</xdr:rowOff>
+      <xdr:rowOff>2313720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2795,7 +2795,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="20969640"/>
-          <a:ext cx="4782600" cy="2314080"/>
+          <a:ext cx="4782240" cy="2313720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2817,9 +2817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843800</xdr:colOff>
+      <xdr:colOff>4843440</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>2165040</xdr:rowOff>
+      <xdr:rowOff>2164680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2833,7 +2833,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29299320" y="24704640"/>
-          <a:ext cx="4771800" cy="2165040"/>
+          <a:ext cx="4771440" cy="2164680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2860,9 +2860,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2896200</xdr:colOff>
+      <xdr:colOff>2895840</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2093400</xdr:rowOff>
+      <xdr:rowOff>2093040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2876,7 +2876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="0"/>
-          <a:ext cx="2896200" cy="2093400"/>
+          <a:ext cx="2895840" cy="2093040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2898,9 +2898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4589280</xdr:colOff>
+      <xdr:colOff>4588920</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>2412720</xdr:rowOff>
+      <xdr:rowOff>2412360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2914,7 +2914,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="3029040"/>
-          <a:ext cx="4589280" cy="2412720"/>
+          <a:ext cx="4588920" cy="2412360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2936,9 +2936,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4619520</xdr:colOff>
+      <xdr:colOff>4619160</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2227680</xdr:rowOff>
+      <xdr:rowOff>2227320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2952,7 +2952,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="6878160"/>
-          <a:ext cx="4619520" cy="2227680"/>
+          <a:ext cx="4619160" cy="2227320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2979,9 +2979,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4754160</xdr:colOff>
+      <xdr:colOff>4753800</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2164320</xdr:rowOff>
+      <xdr:rowOff>2163960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2995,7 +2995,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="0"/>
-          <a:ext cx="4754160" cy="2164320"/>
+          <a:ext cx="4753800" cy="2163960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3017,9 +3017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2389320</xdr:colOff>
+      <xdr:colOff>2388960</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2618280</xdr:rowOff>
+      <xdr:rowOff>2617920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3033,7 +3033,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="9611280"/>
-          <a:ext cx="2389320" cy="2618280"/>
+          <a:ext cx="2388960" cy="2617920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3055,9 +3055,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1827360</xdr:colOff>
+      <xdr:colOff>1827000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>2122920</xdr:rowOff>
+      <xdr:rowOff>2122560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3071,7 +3071,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="12677040"/>
-          <a:ext cx="1827360" cy="2122920"/>
+          <a:ext cx="1827000" cy="2122560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3093,9 +3093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2341800</xdr:colOff>
+      <xdr:colOff>2341440</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2646720</xdr:rowOff>
+      <xdr:rowOff>2646360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3109,7 +3109,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="15085080"/>
-          <a:ext cx="2341800" cy="2646720"/>
+          <a:ext cx="2341440" cy="2646360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3131,9 +3131,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2075040</xdr:colOff>
+      <xdr:colOff>2074680</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>2494440</xdr:rowOff>
+      <xdr:rowOff>2494080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3147,7 +3147,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="18180000"/>
-          <a:ext cx="2075040" cy="2494440"/>
+          <a:ext cx="2074680" cy="2494080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3169,9 +3169,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2779920</xdr:colOff>
+      <xdr:colOff>2779560</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1770120</xdr:rowOff>
+      <xdr:rowOff>1769760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3185,7 +3185,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="4785480"/>
-          <a:ext cx="2779920" cy="1770120"/>
+          <a:ext cx="2779560" cy="1769760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3207,9 +3207,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2189520</xdr:colOff>
+      <xdr:colOff>2189160</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1541520</xdr:rowOff>
+      <xdr:rowOff>1541160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3223,7 +3223,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="7211520"/>
-          <a:ext cx="2189520" cy="1541520"/>
+          <a:ext cx="2189160" cy="1541160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3245,9 +3245,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2303640</xdr:colOff>
+      <xdr:colOff>2303280</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>2599200</xdr:rowOff>
+      <xdr:rowOff>2598840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3261,7 +3261,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="21173400"/>
-          <a:ext cx="2303640" cy="2599200"/>
+          <a:ext cx="2303280" cy="2598840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3283,9 +3283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2351520</xdr:colOff>
+      <xdr:colOff>2351160</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>2465640</xdr:rowOff>
+      <xdr:rowOff>2465280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3299,7 +3299,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="24076800"/>
-          <a:ext cx="2351520" cy="2465640"/>
+          <a:ext cx="2351160" cy="2465280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3321,9 +3321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2141640</xdr:colOff>
+      <xdr:colOff>2141280</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>2465640</xdr:rowOff>
+      <xdr:rowOff>2465280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3337,7 +3337,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="26878320"/>
-          <a:ext cx="2141640" cy="2465640"/>
+          <a:ext cx="2141280" cy="2465280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3359,9 +3359,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2113200</xdr:colOff>
+      <xdr:colOff>2112840</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>2456280</xdr:rowOff>
+      <xdr:rowOff>2455920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3375,7 +3375,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="29679840"/>
-          <a:ext cx="2113200" cy="2456280"/>
+          <a:ext cx="2112840" cy="2455920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3397,9 +3397,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2113200</xdr:colOff>
+      <xdr:colOff>2112840</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>2522880</xdr:rowOff>
+      <xdr:rowOff>2522520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3413,7 +3413,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="32496120"/>
-          <a:ext cx="2113200" cy="2522880"/>
+          <a:ext cx="2112840" cy="2522520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3435,9 +3435,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1999080</xdr:colOff>
+      <xdr:colOff>1998720</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>2370600</xdr:rowOff>
+      <xdr:rowOff>2370240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3451,7 +3451,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="35517960"/>
-          <a:ext cx="1999080" cy="2370600"/>
+          <a:ext cx="1998720" cy="2370240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3473,9 +3473,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2475360</xdr:colOff>
+      <xdr:colOff>2475000</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>2551320</xdr:rowOff>
+      <xdr:rowOff>2550960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3489,7 +3489,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="38261160"/>
-          <a:ext cx="2475360" cy="2551320"/>
+          <a:ext cx="2475000" cy="2550960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3511,9 +3511,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1941840</xdr:colOff>
+      <xdr:colOff>1941480</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2570400</xdr:rowOff>
+      <xdr:rowOff>2570040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3527,7 +3527,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="41193720"/>
-          <a:ext cx="1941840" cy="2570400"/>
+          <a:ext cx="1941480" cy="2570040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3549,9 +3549,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4662720</xdr:colOff>
+      <xdr:colOff>4662360</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>2763000</xdr:rowOff>
+      <xdr:rowOff>2762640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3565,7 +3565,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="45722520"/>
-          <a:ext cx="4662720" cy="2763000"/>
+          <a:ext cx="4662360" cy="2762640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3587,9 +3587,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3723120</xdr:colOff>
+      <xdr:colOff>3722760</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1818000</xdr:rowOff>
+      <xdr:rowOff>1817640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,7 +3603,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="49140720"/>
-          <a:ext cx="3723120" cy="1818000"/>
+          <a:ext cx="3722760" cy="1817640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3625,9 +3625,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4766400</xdr:colOff>
+      <xdr:colOff>4766040</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>2832120</xdr:rowOff>
+      <xdr:rowOff>2831760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3641,7 +3641,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="51640200"/>
-          <a:ext cx="4766400" cy="2832120"/>
+          <a:ext cx="4766040" cy="2831760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3663,9 +3663,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4709160</xdr:colOff>
+      <xdr:colOff>4708800</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>2797920</xdr:rowOff>
+      <xdr:rowOff>2797560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,7 +3679,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="55145880"/>
-          <a:ext cx="4709160" cy="2797920"/>
+          <a:ext cx="4708800" cy="2797560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3825,22 +3825,20 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="F1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3854,7 +3852,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3879,7 +3877,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3893,7 +3891,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3918,7 +3916,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,7 +3930,7 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3946,7 +3944,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3960,7 +3958,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="202.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3996,7 +3994,7 @@
         <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4010,7 +4008,7 @@
         <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4024,7 +4022,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4038,7 +4036,7 @@
         <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4063,7 +4061,7 @@
         <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4077,7 +4075,7 @@
         <v>60</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4102,7 +4100,7 @@
         <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4116,7 +4114,7 @@
         <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4130,7 +4128,7 @@
         <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4155,7 +4153,7 @@
         <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4169,7 +4167,7 @@
         <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4183,7 +4181,7 @@
         <v>84</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4208,7 +4206,7 @@
         <v>90</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4222,7 +4220,7 @@
         <v>93</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4236,7 +4234,7 @@
         <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4261,7 +4259,7 @@
         <v>102</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4286,7 +4284,7 @@
         <v>108</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4311,7 +4309,7 @@
         <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4325,7 +4323,7 @@
         <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4350,7 +4348,7 @@
         <v>123</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4364,7 +4362,7 @@
         <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4389,7 +4387,7 @@
         <v>132</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4403,7 +4401,7 @@
         <v>135</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4417,7 +4415,7 @@
         <v>138</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4442,7 +4440,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,7 +4454,7 @@
         <v>147</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4470,7 +4468,7 @@
         <v>150</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4495,7 +4493,7 @@
         <v>156</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4509,7 +4507,7 @@
         <v>159</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4523,7 +4521,7 @@
         <v>162</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4548,7 +4546,7 @@
         <v>168</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4562,7 +4560,7 @@
         <v>171</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4576,7 +4574,7 @@
         <v>174</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,7 +4599,7 @@
         <v>180</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4615,7 +4613,7 @@
         <v>183</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4629,7 +4627,7 @@
         <v>186</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4643,7 +4641,7 @@
         <v>189</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,7 +4655,7 @@
         <v>192</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4671,7 +4669,7 @@
         <v>195</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="198.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4696,7 +4694,7 @@
         <v>201</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4710,7 +4708,7 @@
         <v>204</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4724,7 +4722,7 @@
         <v>207</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4738,7 +4736,7 @@
         <v>210</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4752,7 +4750,7 @@
         <v>213</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4766,7 +4764,7 @@
         <v>216</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4780,7 +4778,7 @@
         <v>219</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="200.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4805,7 +4803,7 @@
         <v>225</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4819,7 +4817,7 @@
         <v>228</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4833,7 +4831,7 @@
         <v>231</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4847,7 +4845,7 @@
         <v>234</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4861,7 +4859,7 @@
         <v>237</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4875,7 +4873,7 @@
         <v>240</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4900,7 +4898,7 @@
         <v>246</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4914,7 +4912,7 @@
         <v>249</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4928,7 +4926,7 @@
         <v>252</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4942,7 +4940,7 @@
         <v>255</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="191.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4967,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4981,7 +4979,7 @@
         <v>264</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4995,7 +4993,7 @@
         <v>267</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,7 +5007,7 @@
         <v>270</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5023,7 +5021,7 @@
         <v>273</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5037,7 +5035,7 @@
         <v>276</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5051,7 +5049,7 @@
         <v>279</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5065,7 +5063,7 @@
         <v>282</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="183.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5090,7 +5088,7 @@
         <v>288</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5104,7 +5102,7 @@
         <v>291</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5118,7 +5116,7 @@
         <v>294</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5169,7 +5167,7 @@
         <v>300</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5183,7 +5181,7 @@
         <v>303</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,7 +5195,7 @@
         <v>306</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5211,7 +5209,7 @@
         <v>309</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5225,7 +5223,7 @@
         <v>312</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="213.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5250,7 +5248,7 @@
         <v>318</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5264,7 +5262,7 @@
         <v>321</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5278,7 +5276,7 @@
         <v>324</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5292,7 +5290,7 @@
         <v>327</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5306,7 +5304,7 @@
         <v>330</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5320,7 +5318,7 @@
         <v>333</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5334,7 +5332,7 @@
         <v>336</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="185.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5359,7 +5357,7 @@
         <v>342</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5373,7 +5371,7 @@
         <v>345</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5387,7 +5385,7 @@
         <v>348</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5401,7 +5399,7 @@
         <v>351</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5452,7 +5450,7 @@
         <v>357</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5466,7 +5464,7 @@
         <v>360</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5480,7 +5478,7 @@
         <v>363</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,7 +5492,7 @@
         <v>366</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5508,7 +5506,7 @@
         <v>369</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5533,7 +5531,7 @@
         <v>375</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5547,7 +5545,7 @@
         <v>378</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5561,7 +5559,7 @@
         <v>381</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5575,7 +5573,7 @@
         <v>384</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5589,7 +5587,7 @@
         <v>387</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5614,7 +5612,7 @@
         <v>393</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,7 +5626,7 @@
         <v>396</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5642,7 +5640,7 @@
         <v>399</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="152.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5667,7 +5665,7 @@
         <v>405</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5681,7 +5679,7 @@
         <v>408</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5695,7 +5693,7 @@
         <v>411</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="137.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5720,7 +5718,7 @@
         <v>417</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5734,7 +5732,7 @@
         <v>420</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5748,7 +5746,7 @@
         <v>423</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5762,7 +5760,7 @@
         <v>426</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5787,7 +5785,7 @@
         <v>432</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5801,7 +5799,7 @@
         <v>435</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="176.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5826,7 +5824,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5851,7 +5849,7 @@
         <v>447</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5865,7 +5863,7 @@
         <v>450</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="210.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5890,7 +5888,7 @@
         <v>456</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5904,7 +5902,7 @@
         <v>459</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5929,7 +5927,7 @@
         <v>465</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="207.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5954,7 +5952,7 @@
         <v>471</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="207.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5979,7 +5977,7 @@
         <v>477</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6004,7 +6002,7 @@
         <v>483</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="212.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6029,7 +6027,7 @@
         <v>489</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6043,7 +6041,7 @@
         <v>492</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="203.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6068,7 +6066,7 @@
         <v>498</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6093,7 +6091,7 @@
         <v>504</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6118,7 +6116,7 @@
         <v>510</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6132,7 +6130,7 @@
         <v>513</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6157,7 +6155,7 @@
         <v>519</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6171,7 +6169,7 @@
         <v>522</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6185,7 +6183,7 @@
         <v>525</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6199,7 +6197,7 @@
         <v>528</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6224,7 +6222,7 @@
         <v>534</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6238,7 +6236,7 @@
         <v>537</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6252,7 +6250,7 @@
         <v>540</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="230.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6277,7 +6275,7 @@
         <v>546</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6291,7 +6289,7 @@
         <v>549</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6305,7 +6303,7 @@
         <v>552</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="158.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6330,7 +6328,7 @@
         <v>558</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6344,7 +6342,7 @@
         <v>561</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6358,7 +6356,7 @@
         <v>564</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="237.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6384,7 +6382,7 @@
         <v>570</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6398,7 +6396,7 @@
         <v>573</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6412,7 +6410,7 @@
         <v>576</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="234.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6438,7 +6436,7 @@
         <v>582</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6452,7 +6450,7 @@
         <v>585</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6478,7 +6476,7 @@
         <v>591</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6492,7 +6490,7 @@
         <v>594</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6518,7 +6516,7 @@
         <v>600</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6532,7 +6530,7 @@
         <v>603</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6546,7 +6544,7 @@
         <v>606</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6560,7 +6558,7 @@
         <v>609</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6574,7 +6572,7 @@
         <v>612</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6600,7 +6598,7 @@
         <v>618</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6626,7 +6624,7 @@
         <v>624</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6652,7 +6650,7 @@
         <v>630</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6666,7 +6664,7 @@
         <v>633</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6680,7 +6678,7 @@
         <v>636</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6706,7 +6704,7 @@
         <v>642</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6720,7 +6718,7 @@
         <v>645</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6734,7 +6732,7 @@
         <v>648</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6748,7 +6746,7 @@
         <v>651</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6774,7 +6772,7 @@
         <v>657</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6788,7 +6786,7 @@
         <v>660</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6814,7 +6812,7 @@
         <v>666</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6828,7 +6826,7 @@
         <v>669</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6854,7 +6852,7 @@
         <v>675</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6868,7 +6866,7 @@
         <v>678</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6894,7 +6892,7 @@
         <v>684</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6908,7 +6906,7 @@
         <v>687</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6922,7 +6920,7 @@
         <v>690</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6936,7 +6934,7 @@
         <v>693</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6950,7 +6948,7 @@
         <v>696</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6964,7 +6962,7 @@
         <v>699</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6978,7 +6976,7 @@
         <v>702</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6992,7 +6990,7 @@
         <v>705</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7006,7 +7004,7 @@
         <v>708</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7032,7 +7030,7 @@
         <v>714</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7046,7 +7044,7 @@
         <v>717</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7060,7 +7058,7 @@
         <v>720</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7074,7 +7072,7 @@
         <v>723</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7088,7 +7086,7 @@
         <v>726</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7102,7 +7100,7 @@
         <v>729</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7126,18 +7124,18 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="89.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="115.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="96.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="115.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="96.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>732</v>
       </c>
     </row>
@@ -7145,38 +7143,38 @@
       <c r="A2" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>3</v>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>3</v>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>741</v>
       </c>
     </row>
@@ -7184,52 +7182,52 @@
       <c r="A5" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>3</v>
+      <c r="F5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>3</v>
+      <c r="F6" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>3</v>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>753</v>
       </c>
     </row>
@@ -7237,38 +7235,38 @@
       <c r="A9" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>3</v>
+      <c r="F9" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>3</v>
+      <c r="F10" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>762</v>
       </c>
     </row>
@@ -7276,66 +7274,66 @@
       <c r="A12" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>3</v>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="F13" s="0" t="s">
-        <v>3</v>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>3</v>
+      <c r="F14" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="F15" s="0" t="s">
-        <v>3</v>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>777</v>
       </c>
     </row>
@@ -7343,52 +7341,52 @@
       <c r="A17" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>3</v>
+      <c r="F17" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="F18" s="0" t="s">
-        <v>3</v>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="F19" s="0" t="s">
-        <v>3</v>
+      <c r="F19" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>789</v>
       </c>
     </row>
@@ -7396,52 +7394,52 @@
       <c r="A21" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="F21" s="0" t="s">
-        <v>3</v>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="F22" s="0" t="s">
-        <v>3</v>
+      <c r="F22" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="F23" s="0" t="s">
-        <v>3</v>
+      <c r="F23" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>801</v>
       </c>
     </row>
@@ -7449,38 +7447,38 @@
       <c r="A25" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="F25" s="0" t="s">
-        <v>3</v>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D26" s="0" t="s">
+      <c r="D26" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="F26" s="0" t="s">
-        <v>3</v>
+      <c r="F26" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="D27" s="0" t="s">
+      <c r="D27" s="1" t="s">
         <v>810</v>
       </c>
     </row>
@@ -7488,38 +7486,38 @@
       <c r="A28" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="F28" s="0" t="s">
-        <v>3</v>
+      <c r="F28" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="D29" s="0" t="s">
+      <c r="D29" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="F29" s="0" t="s">
-        <v>3</v>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" s="1" t="s">
         <v>819</v>
       </c>
     </row>
@@ -7527,38 +7525,38 @@
       <c r="A31" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="F31" s="0" t="s">
-        <v>3</v>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="F32" s="0" t="s">
-        <v>3</v>
+      <c r="F32" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>828</v>
       </c>
     </row>
@@ -7566,70 +7564,70 @@
       <c r="A34" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="F34" s="0" t="s">
-        <v>3</v>
+      <c r="F34" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="F35" s="0" t="s">
-        <v>3</v>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="F36" s="0" t="s">
-        <v>3</v>
+      <c r="F36" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="F37" s="0" t="s">
-        <v>3</v>
+      <c r="F37" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="F38" s="0" t="s">
-        <v>3</v>
+      <c r="F38" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7651,11 +7649,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="81.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="81.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>844</v>
       </c>
     </row>

--- a/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
+++ b/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
@@ -24,909 +24,927 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="845">
-  <si>
-    <t xml:space="preserve">Data structures are the fundamental building blocks of computer programming.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las estructuras de datos son los componentes básicos de la programación informática.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈdeɪtə ˈstrʌkʧərz ɑr ðə ˌfʌndəˈmɛntəl ˈbɪldɪŋ blɑks ʌv kəmˈpjutər ˈproʊˌɡræmɪŋ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">They define how data is organized, stored, and manipulated within a program.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Definen cómo se organizan, almacenan y manipulan los datos dentro de un programa.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðeɪ dɪˈfaɪn haʊ ˈdeɪtə ɪz ˈɔrɡəˌnaɪzd, stɔrd, ænd məˈnɪpjəˌleɪtɪd wɪˈðɪn ə ˈproʊˌɡræm.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="614">
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Data structures are the fundamental building blocks of computer programming.
+They define how data is organized, stored, and manipulated within a program.
+Understanding data structures is very important for developing efficient and effective algorithms.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Las estructuras de datos son los componentes básicos de la programación informática.
+Definen cómo se organizan, almacenan y manipulan los datos dentro de un programa.
+Comprender las estructuras de datos es muy importante para desarrollar algoritmos eficientes y efectivos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈdeɪtə ˈstrʌkʧərz ɑr ðə ˌfʌndəˈmɛntəl ˈbɪldɪŋ blɑks ʌv kəmˈpjutər ˈproʊˌɡræmɪŋ.
+ðeɪ dɪˈfaɪn haʊ ˈdeɪtə ɪz ˈɔrɡəˌnaɪzd, stɔrd, ænd məˈnɪpjəˌleɪtɪd wɪˈðɪn ə ˈproʊˌɡræm.
+ˌʌndərˈstændɪŋ ˈdeɪtə ˈstrʌkʧərz ɪz ˈvɛri ɪmˈpɔrtənt fɔr dɪˈvɛləpɪŋ ɪˈfɪʃənt ænd ɪˈfɛktɪv ˈælɡəˌrɪðəmz.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">What is Data Structure?
+A data structure is a storage that is used to store and organize data.
+It is a way of arranging data on a computer so that it can be accessed and updated efficiently.
+A data structure is not only used for organizing the data.
+It is also used for processing, retrieving, and storing data.
+There are different basic and advanced types of data structures that are used in almost every program
+or software system that has been developed.
+So we must have good knowledge about data structures.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">¿Qué es una estructura de datos?
+Una estructura de datos es un almacenamiento que se utiliza para almacenar y organizar datos.
+Es una forma de organizar los datos en una computadora para que se pueda acceder a ellos y actualizarlos de manera eficiente.
+Una estructura de datos no solo se utiliza para organizar los datos.
+También se utiliza para procesar, recuperar y almacenar datos.
+Existen diferentes tipos básicos y avanzados de estructuras de datos que se utilizan en casi todos los programas
+o sistemas de software que se han desarrollado.
+Por lo tanto, debemos tener un buen conocimiento sobre las estructuras de datos.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">wɑt ɪz ˈdeɪtə ˈstrʌkʧər?
+ə ˈdeɪtə ˈstrʌkʧər ɪz ə ˈstɔrəʤ ðæt ɪz juzd tu stɔr ænd ˈɔrɡəˌnaɪz ˈdeɪtə.
+ɪt ɪz ə weɪ ʌv əˈreɪnʤɪŋ ˈdeɪtə ɑn ə kəmˈpjutər soʊ ðæt ɪt kæn bi ˈækˌsɛst ænd əpˈdeɪtɪd ɪˈfɪʃəntli.
+ə ˈdeɪtə ˈstrʌkʧər ɪz nɑt ˈoʊnli juzd fɔr ˈɔrɡəˌnaɪzɪŋ ðə ˈdeɪtə.
+ɪt ɪz ˈɔlsoʊ juzd fɔr ˈprɑsɛsɪŋ, riˈtrivɪŋ, ænd ˈstɔrɪŋ ˈdeɪtə.
+ðɛr ɑr ˈdɪfərənt ˈbeɪsɪk ænd ədˈvænst taɪps ʌv ˈdeɪtə ˈstrʌkʧərz ðæt ɑr juzd ɪn ˈɔlˌmoʊst ˈɛvəri ˈproʊˌɡræm
+ɔr ˈsɔfˌtwɛr ˈsɪstəm ðæt hæz bɪn dɪˈvɛləpt.
+soʊ wi mʌst hæv ɡʊd ˈnɑləʤ əˈbaʊt ˈdeɪtə ˈstrʌkʧərz.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Classification of Data Structure
+Linear Data Structure:
+Data structure in which data elements are arranged sequentially or linearly,
+where each element is attached to its previous and next adjacent elements,
+is called a linear data structure.
+Example: Array, Stack, Queue, Linked List, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Clasificación de la estructura de datos
+Estructura de datos lineal:
+Estructura de datos en la que los elementos de datos se organizan de forma secuencial o lineal,
+donde cada elemento está unido a sus elementos adyacentes anterior y siguiente,
+se denomina estructura de datos lineal.
+Ejemplo: matriz, pila, cola, lista enlazada, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ˌklæsəfəˈkeɪʃən ʌv ˈdeɪtə ˈstrʌkʧər
+ˈlɪniər ˈdeɪtə ˈstrʌkʧər:
+ˈdeɪtə ˈstrʌkʧər ɪn wɪʧ ˈdeɪtə ˈɛləmənts ɑr əˈreɪnʤd səˈkwɛnʧəli ɔr ˈlɪniərli,
+wɛr iʧ ˈɛləmənt ɪz əˈtæʧt tu ɪts ˈpriviəs ænd nɛkst əˈʤeɪsənt ˈɛləmənts,
+ɪz kɔld ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər.
+ɪɡˈzæmpəl: əˈreɪ, stæk, kju, lɪŋkt lɪst, ˌɛtˈsɛtərə.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Static Data Structure: Static data structure has a fixed memory size.
+It is easier to access the elements in a static data structure.
+Example: array.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos estática: la estructura de datos estática tiene un tamaño de memoria fijo.
+Es más fácil acceder a los elementos en una estructura de datos estática.
+Ejemplo: matriz.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ˈstætɪk ˈdeɪtə ˈstrʌkʧər: ˈstætɪk ˈdeɪtə ˈstrʌkʧər hæz ə fɪkst ˈmɛməri saɪz.
+ɪt ɪz ˈiziər tu ˈækˌsɛs ði ˈɛləmənts ɪn ə ˈstætɪk ˈdeɪtə ˈstrʌkʧər.
+ɪɡˈzæmpəl: əˈreɪ.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Dynamic Data Structure: In dynamic data structure, the size is not fixed.
+It can be randomly updated during the runtime
+which may be considered efficient concerning the memory (space) complexity of the code.
+Example: Queue, Stack, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos dinámica: en la estructura de datos dinámica, el tamaño no es fijo.
+Se puede actualizar aleatoriamente durante el tiempo de ejecución,
+lo que puede considerarse eficiente en relación con la complejidad de la memoria (espacio) del código.
+Ejemplo: cola, pila, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">daɪˈnæmɪk ˈdeɪtə ˈstrʌkʧər: ɪn daɪˈnæmɪk ˈdeɪtə ˈstrʌkʧər, ðə saɪz ɪz nɑt fɪkst.
+ɪt kæn bi ˈrændəmli əpˈdeɪtɪd ˈdʊrɪŋ ðə runtime
+wɪʧ meɪ bi kənˈsɪdərd ɪˈfɪʃənt kənˈsɜrnɪŋ ðə ˈmɛməri (speɪs) kəmˈplɛksəti ʌv ðə koʊd.
+ɪɡˈzæmpəl: kju, stæk, ˌɛtˈsɛtərə.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Non-Linear Data Structure: Data structures where data elements are not placed sequentially
+or linearly are called non-linear data structures.
+In a non-linear data structure, we can’t traverse all the elements in a single run only.
+Examples: Trees and Graphs.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos no lineal: las estructuras de datos en las que los elementos de datos no se colocan secuencialmente
+o linealmente se denominan estructuras de datos no lineales.
+En una estructura de datos no lineal, no podemos recorrer todos los elementos en una sola ejecución.
+Ejemplos: árboles y gráficos.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər: ˈdeɪtə ˈstrʌkʧərz wɛr ˈdeɪtə ˈɛləmənts ɑr nɑt pleɪst səˈkwɛnʧəli
+ɔr ˈlɪniərli ɑr kɔld nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧərz.
+ɪn ə nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər, wi kænt ˈtrævərs ɔl ði ˈɛləmənts ɪn ə ˈsɪŋɡəl rʌn ˈoʊnli.
+ɪɡˈzæmpəlz: triz ænd ɡræfs.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1. Array:
+Array is a linear data structure that stores a collection of elements of the same data type.
+Elements are allocated contiguous memory, allowing for constant-time access.
+Each element has a unique index number.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1. Matriz:
+La matriz es una estructura de datos lineal que almacena una colección de elementos del mismo tipo de datos.
+A los elementos se les asigna memoria contigua, lo que permite un acceso en tiempo constante.
+Cada elemento tiene un número de índice único.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1. əˈreɪ:
+əˈreɪ ɪz ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər ðæt stɔrz ə kəˈlɛkʃən ʌv ˈɛləmənts ʌv ðə seɪm ˈdeɪtə taɪp.
+ˈɛləmənts ɑr ˈæləˌkeɪtɪd kənˈtɪɡjuəs ˈmɛməri, əˈlaʊɪŋ fɔr ˈkɑnstənt-taɪm ˈækˌsɛs.
+iʧ ˈɛləmənt hæz ə juˈnik ˈɪndɛks ˈnʌmbər.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">In this article, we introduce array, implementation in different popular languages,
+its basic operations and commonly seen problems / interview questions.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">En este artículo, presentamos las matrices, su implementación en diferentes lenguajes populares,
+sus operaciones básicas y problemas comunes/preguntas de entrevistas.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ɪn ðɪs ˈɑrtəkəl, wi ˌɪntrəˈdus əˈreɪ, ˌɪmpləmɛnˈteɪʃən ɪn ˈdɪfərənt ˈpɑpjələr ˈlæŋɡwəʤəz,
+ɪts ˈbeɪsɪk ˌɑpəˈreɪʃənz ænd ˈkɑmənli sin ˈprɑbləmz / ˈɪntərˌvju ˈkwɛsʧənz.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">An array stores items (in case of C/C++ and Java Primitive Arrays)
+or their references (in case of Python, JS, Java Non-Primitive) at contiguous locations.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Una matriz almacena elementos (en el caso de matrices primitivas de C/C++ y Java)
+o sus referencias (en el caso de Python, JS, Java no primitivo) en ubicaciones contiguas.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ən əˈreɪ stɔrz ˈaɪtəmz (ɪn keɪs ʌv si/si++ ænd ˈʤɑvə ˈprɪmətɪv əˈreɪz)
+ɔr ðɛr ˈrɛfərənsɪz (ɪn keɪs ʌv ˈpaɪθɑn, ʤeɪ-ɛs, ˈʤɑvə nɑn-ˈprɪmətɪv) æt kənˈtɪɡjuəs loʊˈkeɪʃənz.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">It offers mainly the following advantages over other data structures.
+Random Access :
+i-th item can be accessed in O(1) Time as we have the base address and every item or reference is of same size.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ofrece principalmente las siguientes ventajas sobre otras estructuras de datos.
+Acceso aleatorio:
+se puede acceder al elemento i-ésimo en tiempo O(1) ya que tenemos la dirección base y cada elemento o referencia es del mismo tamaño.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ɪt ˈɔfərz ˈmeɪnli ðə ˈfɑloʊɪŋ ædˈvæntɪʤɪz ˈoʊvər ˈʌðər ˈdeɪtə ˈstrʌkʧərz.
+ˈrændəm ˈækˌsɛs :
+aɪ-ˈtiˈeɪʧ ˈaɪtəm kæn bi ˈækˌsɛst ɪn oʊ(1) taɪm æz wi hæv ðə beɪs ˈæˌdrɛs ænd ˈɛvəri ˈaɪtəm ɔr ˈrɛfərəns ɪz ʌv seɪm saɪz.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cache Friendliness :
+Since items / references are stored at contiguous locations,
+we get the advantage of locality of reference.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Compatibilidad con la memoria caché:
+ya que los elementos/referencias se almacenan en ubicaciones contiguas,
+obtenemos la ventaja de la localidad de referencia.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">kæʃ ˈfrɛndlinɪs :
+sɪns ˈaɪtəmz / ˈrɛfərənsɪz ɑr stɔrd æt kənˈtɪɡjuəs loʊˈkeɪʃənz,
+wi ɡɛt ði ædˈvæntɪʤ ʌv loʊˈkæləti ʌv ˈrɛfərəns.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">It is not useful in places where we have operations like insert in the middle,
+delete from middle and search in a unsorted data.
+It is a fundamental and linear data structure using which we build -
+- other data structures like Stack Queue, Deque, Graph, Hash Table, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">No es útil en lugares donde tenemos operaciones como insertar en el medio,
+eliminar desde el medio y buscar en datos no ordenados.
+Es una estructura de datos fundamental y lineal que utilizamos para construir
+-otras estructuras de datos como Stack Queue, Deque, Graph, Hash Table, etc.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ɪt ɪz nɑt ˈjusfəl ɪn ˈpleɪsəz wɛr wi hæv ˌɑpəˈreɪʃənz laɪk ɪnˈsɜrt ɪn ðə ˈmɪdəl,
+dɪˈlit frʌm ˈmɪdəl ænd sɜrʧ ɪn ə ʌnˈsɔrtɪd ˈdeɪtə.
+ɪt ɪz ə ˌfʌndəˈmɛntəl ænd ˈlɪniər ˈdeɪtə ˈstrʌkʧər ˈjuzɪŋ wɪʧ wi bɪld -
+- ˈʌðər ˈdeɪtə ˈstrʌkʧərz laɪk stæk kju, Deque, ɡræf, hæʃ ˈteɪbəl, ˌɛtˈsɛtərə.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2. Matrix/Grid
+Matrix is a two-dimensional array of elements, arranged in rows and columns.
+It is represented as a rectangular grid,
+with each element at the intersection of a row and column.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2. Matriz/Cuadrícula
+La matriz es una matriz bidimensional de elementos, dispuestos en filas y columnas.
+Se representa como una cuadrícula rectangular,
+con cada elemento en la intersección de una fila y una columna.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">2. ˈmeɪtrɪks/ɡrɪd
+ˈmeɪtrɪks ɪz ə tu-dɪˈmɛnʃənəl əˈreɪ ʌv ˈɛləmənts, əˈreɪnʤd ɪn roʊz ænd ˈkɑləmz.
+ɪt ɪz ˌrɛprɪˈzɛntɪd æz ə rɛkˈtæŋɡjələr ɡrɪd,
+wɪð iʧ ˈɛləmənt æt ði ˌɪntərˈsɛkʃən ʌv ə roʊ ænd ˈkɑləm.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Matrix Data Structure is a two-dimensional array arranged in rows and columns.
+It is commonly used to represent mathematical matrices and is fundamental in various fields like mathematics,
+computer graphics, and data processing.
+Matrices allow for efficient storage and manipulation of data in a structured format.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">La estructura de datos de matriz es una matriz bidimensional dispuesta en filas y columnas.
+Se utiliza comúnmente para representar matrices matemáticas y es fundamental en varios campos como las matemáticas,
+los gráficos de computadora y el procesamiento de datos.
+Las matrices permiten el almacenamiento y la manipulación eficiente de datos en un formato estructurado.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ˈmeɪtrɪks ˈdeɪtə ˈstrʌkʧər ɪz ə tu-dɪˈmɛnʃənəl əˈreɪ əˈreɪnʤd ɪn roʊz ænd ˈkɑləmz.
+ɪt ɪz ˈkɑmənli juzd tu ˌrɛprəˈzɛnt ˌmæθəˈmætɪkəl ˈmeɪtrɪsɪz ænd ɪz ˌfʌndəˈmɛntəl ɪn ˈvɛriəs fildz laɪk ˌmæθəˈmætɪks,
+kəmˈpjutər ˈɡræfɪks, ænd ˈdeɪtə ˈprɑsɛsɪŋ.
+ˈmeɪtrɪsɪz əˈlaʊ fɔr ɪˈfɪʃənt ˈstɔrəʤ ænd məˌnɪpjəˈleɪʃən ʌv ˈdeɪtə ɪn ə ˈstrʌkʧərd ˈfɔrˌmæt.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">3. String
+String is a sequence of characters, typically used to represent text.
+It is considered a data type that allows for the manipulation -
+- and processing of textual data in computer programs.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">3. Cadena
+La cadena es una secuencia de caracteres, que se utiliza normalmente para representar texto.
+Se considera un tipo de datos que permite la manipulación -
+y el procesamiento de datos textuales en programas informáticos.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">3. strɪŋ
+strɪŋ ɪz ə ˈsikwəns ʌv ˈkærɪktərz, ˈtɪpɪkli juzd tu ˌrɛprəˈzɛnt tɛkst.
+ɪt ɪz kənˈsɪdərd ə ˈdeɪtə taɪp ðæt əˈlaʊz fɔr ðə məˌnɪpjəˈleɪʃən -
+- ænd ˈprɑsɛsɪŋ ʌv ˈtɛksʧəwəl ˈdeɪtə ɪn kəmˈpjutər ˈproʊˌɡræmz.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">A string is a sequence of characters. The following facts make string an interesting data structure.
+Small set of elements. Unlike normal array, strings typically have smaller set of items.
+For example, lowercase English alphabet has only 26 characters. ASCII has only 256 characters.
+Strings are immutable in programming languages like Java, Python, JavaScript and C#.
+Many String Problems can optimized using the fact that the character set size is small.
+For example sorting can be done faster, counting frequencies of items is faster -
+- and many interesting interview questions are based on this.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Una cadena es una secuencia de caracteres. Los siguientes hechos hacen que la cadena sea una estructura de datos interesante.
+Conjunto pequeño de elementos. A diferencia de una matriz normal, las cadenas suelen tener un conjunto de elementos más pequeño.
+Por ejemplo, el alfabeto inglés en minúsculas tiene solo 26 caracteres. El ASCII tiene solo 256 caracteres.
+Las cadenas son inmutables en lenguajes de programación como Java, Python, JavaScript y C#.
+Muchos problemas de cadenas se pueden optimizar utilizando el hecho de que el tamaño del conjunto de caracteres es pequeño.
+Por ejemplo, la clasificación se puede realizar más rápido, el conteo de frecuencias de elementos es más rápido -
+- y muchas preguntas de entrevistas interesantes se basan en esto.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ə strɪŋ ɪz ə ˈsikwəns ʌv ˈkærɪktərz. ðə ˈfɑloʊɪŋ fækts meɪk strɪŋ ən ˈɪntrəstɪŋ ˈdeɪtə ˈstrʌkʧər.
+smɔl sɛt ʌv ˈɛləmənts. ənˈlaɪk ˈnɔrməl əˈreɪ, strɪŋz ˈtɪpɪkli hæv ˈsmɔlər sɛt ʌv ˈaɪtəmz.
+fɔr ɪɡˈzæmpəl, lowercase ˈɪŋɡlɪʃ ˈælfəˌbɛt hæz ˈoʊnli 26 ˈkærɪktərz. ˈæski hæz ˈoʊnli 256 ˈkærɪktərz.
+strɪŋz ɑr ɪmˈjutəbəl ɪn ˈproʊˌɡræmɪŋ ˈlæŋɡwəʤəz laɪk ˈʤɑvə, ˈpaɪθɑn, ˈʤɑvəˌskrɪpt ænd si#.
+ˈmɛni strɪŋ ˈprɑbləmz kæn ˈɑptəˌmaɪzd ˈjuzɪŋ ðə fækt ðæt ðə ˈkɛrɪktər sɛt saɪz ɪz smɔl.
+fɔr ɪɡˈzæmpəl ˈsɔrtɪŋ kæn bi dʌn ˈfæstər, ˈkaʊntɪŋ ˈfrikwənsiz ʌv ˈaɪtəmz ɪz ˈfæstər -
+- ænd ˈmɛni ˈɪntrəstɪŋ ˈɪntərˌvju ˈkwɛsʧənz ɑr beɪst ɑn ðɪs.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">4. Stack
+A Stack is a linear data structure that follows a particular order in which the operations are performed.
+The order may be LIFO(Last In First Out) or FILO(First In Last Out).
+LIFO implies that the element that is inserted last,
+comes out first and FILO implies that the element that is inserted first, comes out last.
+It behaves like a stack of plates, where the last plate added is the first one to be removed. Think of it this way:
+Pushing an element onto the stack is like adding a new plate on top.
+Popping an element removes the top plate from the stack.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">4. Pila
+Una pila es una estructura de datos lineal que sigue un orden particular en el que se realizan las operaciones.
+El orden puede ser LIFO (último en entrar, primero en salir) o FILO (primero en entrar, último en salir).
+LIFO implica que el elemento que se inserta último,
+sale primero y FILO implica que el elemento que se inserta primero, sale último.
+Se comporta como una pila de platos, donde el último plato agregado es el primero en ser eliminado. Piénselo de esta manera:
+Empujar un elemento en la pila es como agregar un nuevo plato en la parte superior.
+Al sacar un elemento, se quita el plato superior de la pila.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">4. stæk
+ə stæk ɪz ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər ðæt ˈfɑloʊz ə pərˈtɪkjələr ˈɔrdər ɪn wɪʧ ði ˌɑpəˈreɪʃənz ɑr pərˈfɔrmd.
+ði ˈɔrdər meɪ bi ˈlifoʊ(læst ɪn fɜrst aʊt) ɔr ˈfiloʊ(fɜrst ɪn læst aʊt).
+ˈlifoʊ ɪmˈplaɪz ðæt ði ˈɛləmənt ðæt ɪz ɪnˈsɜrtɪd læst,
+kʌmz aʊt fɜrst ænd ˈfiloʊ ɪmˈplaɪz ðæt ði ˈɛləmənt ðæt ɪz ɪnˈsɜrtɪd fɜrst, kʌmz aʊt læst.
+ɪt bɪˈheɪvz laɪk ə stæk ʌv pleɪts, wɛr ðə læst pleɪt ˈædɪd ɪz ðə fɜrst wʌn tu bi riˈmuvd. θɪŋk ʌv ɪt ðɪs weɪ:
+ˈpʊʃɪŋ ən ˈɛləmənt ˈɑntu ðə stæk ɪz laɪk ˈædɪŋ ə nu pleɪt ɑn tɑp.
+ˈpɑpɪŋ ən ˈɛləmənt riˈmuvz ðə tɑp pleɪt frʌm ðə stæk.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Queue Data Structure
+A Queue Data Structure is a fundamental concept in computer science -
+-used for storing and managing data in a specific order.
+It follows the principle of "First in, First out" (FIFO),
+where the first element added to the queue is the first one to be removed.
+Queues are commonly used in various algorithms
+and applications for their simplicity and efficiency in managing data flow.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos de cola
+Una estructura de datos de cola es un concepto fundamental en informática:
+se utiliza para almacenar y gestionar datos en un orden específico.
+Sigue el principio de "primero en entrar, primero en salir" (FIFO),
+donde el primer elemento añadido a la cola es el primero en eliminarse.
+Las colas se utilizan comúnmente en varios algoritmos
+y aplicaciones por su simplicidad y eficiencia en la gestión del flujo de datos.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">kju ˈdeɪtə ˈstrʌkʧər
+ə kju ˈdeɪtə ˈstrʌkʧər ɪz ə ˌfʌndəˈmɛntəl ˈkɑnsɛpt ɪn kəmˈpjutər ˈsaɪəns -
+-juzd fɔr ˈstɔrɪŋ ænd ˈmænəʤɪŋ ˈdeɪtə ɪn ə spəˈsɪfɪk ˈɔrdər.
+ɪt ˈfɑloʊz ðə ˈprɪnsəpəl ʌv "fɜrst ɪn, fɜrst aʊt" (ɛf-aɪ-ɛf-oʊ),
+wɛr ðə fɜrst ˈɛləmənt ˈædɪd tu ðə kju ɪz ðə fɜrst wʌn tu bi riˈmuvd.
+kjuz ɑr ˈkɑmənli juzd ɪn ˈvɛriəs ˈælɡəˌrɪðəmz
+ænd ˌæpləˈkeɪʃənz fɔr ðɛr sɪmˈplɪsəti ænd ɪˈfɪʃənsi ɪn ˈmænəʤɪŋ ˈdeɪtə floʊ.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Linked List Data Structure
+A linked list is a fundamental data structure in computer science.
+It mainly allows efficient insertion and deletion operations compared to arrays.
+Like arrays, it is also used to implement other data structures like stack, queue and deque.
+Here’s the comparison of Linked List vs Arrays
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos de lista enlazada
+Una lista enlazada es una estructura de datos fundamental en la informática.
+Principalmente, permite operaciones de inserción y eliminación eficientes en comparación con las matrices.
+Al igual que las matrices, también se utiliza para implementar otras estructuras de datos como pila, cola y deque.
+A continuación, se muestra la comparación de lista enlazada frente a matrices
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lɪŋkt lɪst ˈdeɪtə ˈstrʌkʧər
+ə lɪŋkt lɪst ɪz ə ˌfʌndəˈmɛntəl ˈdeɪtə ˈstrʌkʧər ɪn kəmˈpjutər ˈsaɪəns.
+ɪt ˈmeɪnli əˈlaʊz ɪˈfɪʃənt ɪnˈsɜrʃən ænd dɪˈliʃən ˌɑpəˈreɪʃənz kəmˈpɛrd tu əˈreɪz.
+laɪk əˈreɪz, ɪt ɪz ˈɔlsoʊ juzd tu ˈɪmpləˌmɛnt ˈʌðər ˈdeɪtə ˈstrʌkʧərz laɪk stæk, kju ænd deque.
+hɪrz ðə kəmˈpɛrəsən ʌv lɪŋkt lɪst ˈvɜrsəz əˈreɪz
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hashing in Data Structure
+Hashing is a technique used in data structures that efficiently stores
+and retrieves data in a way that allows for quick access.
+Hashing involves mapping data to a specific index in a hash table (an array of items) -
+- using a hash function that enables fast retrieval of information based on its key.
+The great thing about hashing is,
+we can achieve all three operations (search, insert and delete) in O(1) time on average.
+Hashing is mainly used to implement a set of distinct items
+and dictionaries (key value pairs).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Hash en la estructura de datos
+El hash es una técnica utilizada en estructuras de datos que almacena
+y recupera datos de manera eficiente de una manera que permite un acceso rápido.
+El hash implica asignar datos a un índice específico en una tabla hash (una matriz de elementos) -
+- utilizando una función hash que permite la recuperación rápida de información en función de su clave.
+Lo bueno del hash es que
+podemos lograr las tres operaciones (búsqueda, inserción y eliminación) en un tiempo O(1) en promedio.
+El hash se utiliza principalmente para implementar un conjunto de elementos distintos
+y diccionarios (pares clave-valor).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ˈhæʃɪŋ ɪn ˈdeɪtə ˈstrʌkʧər
+ˈhæʃɪŋ ɪz ə tɛkˈnik juzd ɪn ˈdeɪtə ˈstrʌkʧərz ðæt ɪˈfɪʃəntli stɔrz
+ænd rɪˈtrivz ˈdeɪtə ɪn ə weɪ ðæt əˈlaʊz fɔr kwɪk ˈækˌsɛs.
+ˈhæʃɪŋ ɪnˈvɑlvz ˈmæpɪŋ ˈdeɪtə tu ə spəˈsɪfɪk ˈɪndɛks ɪn ə hæʃ ˈteɪbəl (ən əˈreɪ ʌv ˈaɪtəmz) -
+- ˈjuzɪŋ ə hæʃ ˈfʌŋkʃən ðæt ɛˈneɪbəlz fæst rɪˈtrivəl ʌv ˌɪnfərˈmeɪʃən beɪst ɑn ɪts ki.
+ðə ɡreɪt θɪŋ əˈbaʊt ˈhæʃɪŋ ɪz,
+wi kæn əˈʧiv ɔl θri ˌɑpəˈreɪʃənz (sɜrʧ, ɪnˈsɜrt ænd dɪˈlit) ɪn oʊ(1) taɪm ɑn ˈævərɪʤ.
+ˈhæʃɪŋ ɪz ˈmeɪnli juzd tu ˈɪmpləˌmɛnt ə sɛt ʌv dɪˈstɪŋkt ˈaɪtəmz
+ænd ˈdɪkʃəˌnɛriz (ki ˈvælju pɛrz).
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Tree Data Structure
+Tree Data Structure is a non-linear data structure in which a collection of -
+- elements known as nodes are connected to each other via edges such that -
+- there exists exactly one path between any two nodes.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Estructura de datos en forma de árbol
+La estructura de datos en forma de árbol es una estructura de datos no lineal en la que una colección de
+elementos, conocidos como nodos, están conectados entre sí a través de aristas de modo que
+existe exactamente una ruta entre dos nodos cualesquiera.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">tri ˈdeɪtə ˈstrʌkʧər
+tri ˈdeɪtə ˈstrʌkʧər ɪz ə nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər ɪn wɪʧ ə kəˈlɛkʃən ʌv -
+- ˈɛləmənts noʊn æz noʊdz ɑr kəˈnɛktɪd tu iʧ ˈʌðər ˈvaɪə ˈɛʤəz sʌʧ ðæt -
+- ðɛr ɪɡˈzɪsts ɪɡˈzæktli wʌn pæθ bɪˈtwin ˈɛni tu noʊdz.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Tree Data Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estructura de datos de árbol binario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ˈbaɪnəri tri ˈdeɪtə ˈstrʌkʧər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Binary Tree Data Structure is a hierarchical data structure -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una estructura de datos de árbol binario es una estructura de datos jerárquica -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ə ˈbaɪnəri tri ˈdeɪtə ˈstrʌkʧər ɪz ə ˌhaɪˈrɑrkəkəl ˈdeɪtə ˈstrʌkʧər -</t>
   </si>
   <si>
     <t xml:space="preserve">EXAMPLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Understanding data structures is very important for developing efficient and effective algorithms.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprender las estructuras de datos es muy importante para desarrollar algoritmos eficientes y efectivos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˌʌndərˈstændɪŋ ˈdeɪtə ˈstrʌkʧərz ɪz ˈvɛri ɪmˈpɔrtənt fɔr dɪˈvɛləpɪŋ ɪˈfɪʃənt ænd ɪˈfɛktɪv ˈælɡəˌrɪðəmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is Data Structure?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Qué es una estructura de datos?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɑt ɪz ˈdeɪtə ˈstrʌkʧər?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data structure is a storage that is used to store and organize data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una estructura de datos es un almacenamiento que se utiliza para almacenar y organizar datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə ˈdeɪtə ˈstrʌkʧər ɪz ə ˈstɔrəʤ ðæt ɪz juzd tu stɔr ænd ˈɔrɡəˌnaɪz ˈdeɪtə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is a way of arranging data on a computer so that it can be accessed and updated efficiently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es una forma de organizar los datos en una computadora para que se pueda acceder a ellos y actualizarlos de manera eficiente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ə weɪ ʌv əˈreɪnʤɪŋ ˈdeɪtə ɑn ə kəmˈpjutər soʊ ðæt ɪt kæn bi ˈækˌsɛst ænd əpˈdeɪtɪd ɪˈfɪʃəntli.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A data structure is not only used for organizing the data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una estructura de datos no solo se utiliza para organizar los datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə ˈdeɪtə ˈstrʌkʧər ɪz nɑt ˈoʊnli juzd fɔr ˈɔrɡəˌnaɪzɪŋ ðə ˈdeɪtə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is also used for processing, retrieving, and storing data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">También se utiliza para procesar, recuperar y almacenar datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ˈɔlsoʊ juzd fɔr ˈprɑsɛsɪŋ, riˈtrivɪŋ, ænd ˈstɔrɪŋ ˈdeɪtə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are different basic and advanced types of data structures that are used in almost every program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Existen diferentes tipos básicos y avanzados de estructuras de datos que se utilizan en casi todos los programas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðɛr ɑr ˈdɪfərənt ˈbeɪsɪk ænd ədˈvænst taɪps ʌv ˈdeɪtə ˈstrʌkʧərz ðæt ɑr juzd ɪn ˈɔlˌmoʊst ˈɛvəri ˈproʊˌɡræm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">or software system that has been developed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o sistemas de software que se han desarrollado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɔr ˈsɔfˌtwɛr ˈsɪstəm ðæt hæz bɪn dɪˈvɛləpt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">So we must have good knowledge about data structures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por lo tanto, debemos tener un buen conocimiento sobre las estructuras de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">soʊ wi mʌst hæv ɡʊd ˈnɑləʤ əˈbaʊt ˈdeɪtə ˈstrʌkʧərz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classification of Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clasificación de la estructura de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˌklæsəfəˈkeɪʃən ʌv ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear Data Structure:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos lineal:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈlɪniər ˈdeɪtə ˈstrʌkʧər:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data structure in which data elements are arranged sequentially or linearly,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos en la que los elementos de datos se organizan de forma secuencial o lineal,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈdeɪtə ˈstrʌkʧər ɪn wɪʧ ˈdeɪtə ˈɛləmənts ɑr əˈreɪnʤd səˈkwɛnʧəli ɔr ˈlɪniərli,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">where each element is attached to its previous and next adjacent elements,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">donde cada elemento está unido a sus elementos adyacentes anterior y siguiente,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɛr iʧ ˈɛləmənt ɪz əˈtæʧt tu ɪts ˈpriviəs ænd nɛkst əˈʤeɪsənt ˈɛləmənts,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">is called a linear data structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se denomina estructura de datos lineal.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪz kɔld ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: Array, Stack, Queue, Linked List, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplo: matriz, pila, cola, lista enlazada, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪɡˈzæmpəl: əˈreɪ, stæk, kju, lɪŋkt lɪst, ˌɛtˈsɛtərə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Static Data Structure: Static data structure has a fixed memory size.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos estática: la estructura de datos estática tiene un tamaño de memoria fijo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈstætɪk ˈdeɪtə ˈstrʌkʧər: ˈstætɪk ˈdeɪtə ˈstrʌkʧər hæz ə fɪkst ˈmɛməri saɪz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is easier to access the elements in a static data structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es más fácil acceder a los elementos en una estructura de datos estática.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ˈiziər tu ˈækˌsɛs ði ˈɛləmənts ɪn ə ˈstætɪk ˈdeɪtə ˈstrʌkʧər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: array.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplo: matriz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪɡˈzæmpəl: əˈreɪ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Data Structure: In dynamic data structure, the size is not fixed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos dinámica: en la estructura de datos dinámica, el tamaño no es fijo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">daɪˈnæmɪk ˈdeɪtə ˈstrʌkʧər: ɪn daɪˈnæmɪk ˈdeɪtə ˈstrʌkʧər, ðə saɪz ɪz nɑt fɪkst.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It can be randomly updated during the runtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se puede actualizar aleatoriamente durante el tiempo de ejecución,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt kæn bi ˈrændəmli əpˈdeɪtɪd ˈdʊrɪŋ ðə runtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which may be considered efficient concerning the memory (space) complexity of the code.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lo que puede considerarse eficiente en relación con la complejidad de la memoria (espacio) del código.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɪʧ meɪ bi kənˈsɪdərd ɪˈfɪʃənt kənˈsɜrnɪŋ ðə ˈmɛməri (speɪs) kəmˈplɛksəti ʌv ðə koʊd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example: Queue, Stack, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplo: cola, pila, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪɡˈzæmpəl: kju, stæk, ˌɛtˈsɛtərə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-Linear Data Structure: Data structures where data elements are not placed sequentially</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos no lineal: las estructuras de datos en las que los elementos de datos no se colocan secuencialmente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər: ˈdeɪtə ˈstrʌkʧərz wɛr ˈdeɪtə ˈɛləmənts ɑr nɑt pleɪst səˈkwɛnʧəli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">or linearly are called non-linear data structures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o linealmente se denominan estructuras de datos no lineales.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɔr ˈlɪniərli ɑr kɔld nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧərz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In a non-linear data structure, we can’t traverse all the elements in a single run only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En una estructura de datos no lineal, no podemos recorrer todos los elementos en una sola ejecución.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪn ə nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər, wi kænt ˈtrævərs ɔl ði ˈɛləmənts ɪn ə ˈsɪŋɡəl rʌn ˈoʊnli.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Examples: Trees and Graphs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ejemplos: árboles y gráficos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪɡˈzæmpəlz: triz ænd ɡræfs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Array:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Matriz:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. əˈreɪ:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Array is a linear data structure that stores a collection of elements of the same data type.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La matriz es una estructura de datos lineal que almacena una colección de elementos del mismo tipo de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">əˈreɪ ɪz ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər ðæt stɔrz ə kəˈlɛkʃən ʌv ˈɛləmənts ʌv ðə seɪm ˈdeɪtə taɪp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elements are allocated contiguous memory, allowing for constant-time access.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A los elementos se les asigna memoria contigua, lo que permite un acceso en tiempo constante.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈɛləmənts ɑr ˈæləˌkeɪtɪd kənˈtɪɡjuəs ˈmɛməri, əˈlaʊɪŋ fɔr ˈkɑnstənt-taɪm ˈækˌsɛs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Each element has a unique index number.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cada elemento tiene un número de índice único.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iʧ ˈɛləmənt hæz ə juˈnik ˈɪndɛks ˈnʌmbər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In this article, we introduce array, implementation in different popular languages,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En este artículo, presentamos las matrices, su implementación en diferentes lenguajes populares,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪn ðɪs ˈɑrtəkəl, wi ˌɪntrəˈdus əˈreɪ, ˌɪmpləmɛnˈteɪʃən ɪn ˈdɪfərənt ˈpɑpjələr ˈlæŋɡwəʤəz,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">its basic operations and commonly seen problems / interview questions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sus operaciones básicas y problemas comunes/preguntas de entrevistas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪts ˈbeɪsɪk ˌɑpəˈreɪʃənz ænd ˈkɑmənli sin ˈprɑbləmz / ˈɪntərˌvju ˈkwɛsʧənz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">An array stores items (in case of C/C++ and Java Primitive Arrays)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una matriz almacena elementos (en el caso de matrices primitivas de C/C++ y Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ən əˈreɪ stɔrz ˈaɪtəmz (ɪn keɪs ʌv si/si++ ænd ˈʤɑvə ˈprɪmətɪv əˈreɪz)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">or their references (in case of Python, JS, Java Non-Primitive) at contiguous locations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o sus referencias (en el caso de Python, JS, Java no primitivo) en ubicaciones contiguas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɔr ðɛr ˈrɛfərənsɪz (ɪn keɪs ʌv ˈpaɪθɑn, ʤeɪ-ɛs, ˈʤɑvə nɑn-ˈprɪmətɪv) æt kənˈtɪɡjuəs loʊˈkeɪʃənz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It offers mainly the following advantages over other data structures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ofrece principalmente las siguientes ventajas sobre otras estructuras de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ˈɔfərz ˈmeɪnli ðə ˈfɑloʊɪŋ ædˈvæntɪʤɪz ˈoʊvər ˈʌðər ˈdeɪtə ˈstrʌkʧərz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random Access :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acceso aleatorio:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈrændəm ˈækˌsɛs :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i-th item can be accessed in O(1) Time as we have the base address and every item or reference is of same size.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se puede acceder al elemento i-ésimo en tiempo O(1) ya que tenemos la dirección base y cada elemento o referencia es del mismo tamaño.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aɪ-ˈtiˈeɪʧ ˈaɪtəm kæn bi ˈækˌsɛst ɪn oʊ(1) taɪm æz wi hæv ðə beɪs ˈæˌdrɛs ænd ˈɛvəri ˈaɪtəm ɔr ˈrɛfərəns ɪz ʌv seɪm saɪz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cache Friendliness :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compatibilidad con la memoria caché:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kæʃ ˈfrɛndlinɪs :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Since items / references are stored at contiguous locations,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ya que los elementos/referencias se almacenan en ubicaciones contiguas,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sɪns ˈaɪtəmz / ˈrɛfərənsɪz ɑr stɔrd æt kənˈtɪɡjuəs loʊˈkeɪʃənz,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">we get the advantage of locality of reference.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obtenemos la ventaja de la localidad de referencia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wi ɡɛt ði ædˈvæntɪʤ ʌv loʊˈkæləti ʌv ˈrɛfərəns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is not useful in places where we have operations like insert in the middle,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No es útil en lugares donde tenemos operaciones como insertar en el medio,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz nɑt ˈjusfəl ɪn ˈpleɪsəz wɛr wi hæv ˌɑpəˈreɪʃənz laɪk ɪnˈsɜrt ɪn ðə ˈmɪdəl,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delete from middle and search in a unsorted data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eliminar desde el medio y buscar en datos no ordenados.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dɪˈlit frʌm ˈmɪdəl ænd sɜrʧ ɪn ə ʌnˈsɔrtɪd ˈdeɪtə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is a fundamental and linear data structure using which we build -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es una estructura de datos fundamental y lineal que utilizamos para construir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ə ˌfʌndəˈmɛntəl ænd ˈlɪniər ˈdeɪtə ˈstrʌkʧər ˈjuzɪŋ wɪʧ wi bɪld -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- other data structures like Stack Queue, Deque, Graph, Hash Table, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-otras estructuras de datos como Stack Queue, Deque, Graph, Hash Table, etc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ˈʌðər ˈdeɪtə ˈstrʌkʧərz laɪk stæk kju, Deque, ɡræf, hæʃ ˈteɪbəl, ˌɛtˈsɛtərə.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Matrix/Grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Matriz/Cuadrícula</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. ˈmeɪtrɪks/ɡrɪd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix is a two-dimensional array of elements, arranged in rows and columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La matriz es una matriz bidimensional de elementos, dispuestos en filas y columnas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈmeɪtrɪks ɪz ə tu-dɪˈmɛnʃənəl əˈreɪ ʌv ˈɛləmənts, əˈreɪnʤd ɪn roʊz ænd ˈkɑləmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is represented as a rectangular grid,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se representa como una cuadrícula rectangular,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ˌrɛprɪˈzɛntɪd æz ə rɛkˈtæŋɡjələr ɡrɪd,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">with each element at the intersection of a row and column.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">con cada elemento en la intersección de una fila y una columna.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɪð iʧ ˈɛləmənt æt ði ˌɪntərˈsɛkʃən ʌv ə roʊ ænd ˈkɑləm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrix Data Structure is a two-dimensional array arranged in rows and columns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La estructura de datos de matriz es una matriz bidimensional dispuesta en filas y columnas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈmeɪtrɪks ˈdeɪtə ˈstrʌkʧər ɪz ə tu-dɪˈmɛnʃənəl əˈreɪ əˈreɪnʤd ɪn roʊz ænd ˈkɑləmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is commonly used to represent mathematical matrices and is fundamental in various fields like mathematics,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se utiliza comúnmente para representar matrices matemáticas y es fundamental en varios campos como las matemáticas,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz ˈkɑmənli juzd tu ˌrɛprəˈzɛnt ˌmæθəˈmætɪkəl ˈmeɪtrɪsɪz ænd ɪz ˌfʌndəˈmɛntəl ɪn ˈvɛriəs fildz laɪk ˌmæθəˈmætɪks,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">computer graphics, and data processing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">los gráficos de computadora y el procesamiento de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kəmˈpjutər ˈɡræfɪks, ænd ˈdeɪtə ˈprɑsɛsɪŋ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matrices allow for efficient storage and manipulation of data in a structured format.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las matrices permiten el almacenamiento y la manipulación eficiente de datos en un formato estructurado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈmeɪtrɪsɪz əˈlaʊ fɔr ɪˈfɪʃənt ˈstɔrəʤ ænd məˌnɪpjəˈleɪʃən ʌv ˈdeɪtə ɪn ə ˈstrʌkʧərd ˈfɔrˌmæt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. String</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Cadena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. strɪŋ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">String is a sequence of characters, typically used to represent text.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La cadena es una secuencia de caracteres, que se utiliza normalmente para representar texto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strɪŋ ɪz ə ˈsikwəns ʌv ˈkærɪktərz, ˈtɪpɪkli juzd tu ˌrɛprəˈzɛnt tɛkst.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It is considered a data type that allows for the manipulation -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se considera un tipo de datos que permite la manipulación -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ɪz kənˈsɪdərd ə ˈdeɪtə taɪp ðæt əˈlaʊz fɔr ðə məˌnɪpjəˈleɪʃən -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- and processing of textual data in computer programs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y el procesamiento de datos textuales en programas informáticos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ænd ˈprɑsɛsɪŋ ʌv ˈtɛksʧəwəl ˈdeɪtə ɪn kəmˈpjutər ˈproʊˌɡræmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A string is a sequence of characters. The following facts make string an interesting data structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una cadena es una secuencia de caracteres. Los siguientes hechos hacen que la cadena sea una estructura de datos interesante.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə strɪŋ ɪz ə ˈsikwəns ʌv ˈkærɪktərz. ðə ˈfɑloʊɪŋ fækts meɪk strɪŋ ən ˈɪntrəstɪŋ ˈdeɪtə ˈstrʌkʧər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small set of elements. Unlike normal array, strings typically have smaller set of items.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjunto pequeño de elementos. A diferencia de una matriz normal, las cadenas suelen tener un conjunto de elementos más pequeño.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">smɔl sɛt ʌv ˈɛləmənts. ənˈlaɪk ˈnɔrməl əˈreɪ, strɪŋz ˈtɪpɪkli hæv ˈsmɔlər sɛt ʌv ˈaɪtəmz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For example, lowercase English alphabet has only 26 characters. ASCII has only 256 characters.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por ejemplo, el alfabeto inglés en minúsculas tiene solo 26 caracteres. El ASCII tiene solo 256 caracteres.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fɔr ɪɡˈzæmpəl, lowercase ˈɪŋɡlɪʃ ˈælfəˌbɛt hæz ˈoʊnli 26 ˈkærɪktərz. ˈæski hæz ˈoʊnli 256 ˈkærɪktərz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strings are immutable in programming languages like Java, Python, JavaScript and C#.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las cadenas son inmutables en lenguajes de programación como Java, Python, JavaScript y C#.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">strɪŋz ɑr ɪmˈjutəbəl ɪn ˈproʊˌɡræmɪŋ ˈlæŋɡwəʤəz laɪk ˈʤɑvə, ˈpaɪθɑn, ˈʤɑvəˌskrɪpt ænd si#.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Many String Problems can optimized using the fact that the character set size is small.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muchos problemas de cadenas se pueden optimizar utilizando el hecho de que el tamaño del conjunto de caracteres es pequeño.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈmɛni strɪŋ ˈprɑbləmz kæn ˈɑptəˌmaɪzd ˈjuzɪŋ ðə fækt ðæt ðə ˈkɛrɪktər sɛt saɪz ɪz smɔl.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For example sorting can be done faster, counting frequencies of items is faster -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por ejemplo, la clasificación se puede realizar más rápido, el conteo de frecuencias de elementos es más rápido -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fɔr ɪɡˈzæmpəl ˈsɔrtɪŋ kæn bi dʌn ˈfæstər, ˈkaʊntɪŋ ˈfrikwənsiz ʌv ˈaɪtəmz ɪz ˈfæstər -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- and many interesting interview questions are based on this.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- y muchas preguntas de entrevistas interesantes se basan en esto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ænd ˈmɛni ˈɪntrəstɪŋ ˈɪntərˌvju ˈkwɛsʧənz ɑr beɪst ɑn ðɪs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Pila</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. stæk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Stack is a linear data structure that follows a particular order in which the operations are performed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una pila es una estructura de datos lineal que sigue un orden particular en el que se realizan las operaciones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə stæk ɪz ə ˈlɪniər ˈdeɪtə ˈstrʌkʧər ðæt ˈfɑloʊz ə pərˈtɪkjələr ˈɔrdər ɪn wɪʧ ði ˌɑpəˈreɪʃənz ɑr pərˈfɔrmd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The order may be LIFO(Last In First Out) or FILO(First In Last Out).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El orden puede ser LIFO (último en entrar, primero en salir) o FILO (primero en entrar, último en salir).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ði ˈɔrdər meɪ bi ˈlifoʊ(læst ɪn fɜrst aʊt) ɔr ˈfiloʊ(fɜrst ɪn læst aʊt).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIFO implies that the element that is inserted last,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIFO implica que el elemento que se inserta último,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈlifoʊ ɪmˈplaɪz ðæt ði ˈɛləmənt ðæt ɪz ɪnˈsɜrtɪd læst,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comes out first and FILO implies that the element that is inserted first, comes out last.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sale primero y FILO implica que el elemento que se inserta primero, sale último.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kʌmz aʊt fɜrst ænd ˈfiloʊ ɪmˈplaɪz ðæt ði ˈɛləmənt ðæt ɪz ɪnˈsɜrtɪd fɜrst, kʌmz aʊt læst.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It behaves like a stack of plates, where the last plate added is the first one to be removed. Think of it this way:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se comporta como una pila de platos, donde el último plato agregado es el primero en ser eliminado. Piénselo de esta manera:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt bɪˈheɪvz laɪk ə stæk ʌv pleɪts, wɛr ðə læst pleɪt ˈædɪd ɪz ðə fɜrst wʌn tu bi riˈmuvd. θɪŋk ʌv ɪt ðɪs weɪ:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pushing an element onto the stack is like adding a new plate on top.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empujar un elemento en la pila es como agregar un nuevo plato en la parte superior.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈpʊʃɪŋ ən ˈɛləmənt ˈɑntu ðə stæk ɪz laɪk ˈædɪŋ ə nu pleɪt ɑn tɑp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Popping an element removes the top plate from the stack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al sacar un elemento, se quita el plato superior de la pila.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈpɑpɪŋ ən ˈɛləmənt riˈmuvz ðə tɑp pleɪt frʌm ðə stæk.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queue Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos de cola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kju ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Queue Data Structure is a fundamental concept in computer science -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una estructura de datos de cola es un concepto fundamental en informática:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə kju ˈdeɪtə ˈstrʌkʧər ɪz ə ˌfʌndəˈmɛntəl ˈkɑnsɛpt ɪn kəmˈpjutər ˈsaɪəns -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-used for storing and managing data in a specific order.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">se utiliza para almacenar y gestionar datos en un orden específico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-juzd fɔr ˈstɔrɪŋ ænd ˈmænəʤɪŋ ˈdeɪtə ɪn ə spəˈsɪfɪk ˈɔrdər.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It follows the principle of "First in, First out" (FIFO),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sigue el principio de "primero en entrar, primero en salir" (FIFO),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ˈfɑloʊz ðə ˈprɪnsəpəl ʌv "fɜrst ɪn, fɜrst aʊt" (ɛf-aɪ-ɛf-oʊ),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">where the first element added to the queue is the first one to be removed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">donde el primer elemento añadido a la cola es el primero en eliminarse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wɛr ðə fɜrst ˈɛləmənt ˈædɪd tu ðə kju ɪz ðə fɜrst wʌn tu bi riˈmuvd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queues are commonly used in various algorithms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las colas se utilizan comúnmente en varios algoritmos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kjuz ɑr ˈkɑmənli juzd ɪn ˈvɛriəs ˈælɡəˌrɪðəmz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and applications for their simplicity and efficiency in managing data flow.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y aplicaciones por su simplicidad y eficiencia en la gestión del flujo de datos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ænd ˌæpləˈkeɪʃənz fɔr ðɛr sɪmˈplɪsəti ænd ɪˈfɪʃənsi ɪn ˈmænəʤɪŋ ˈdeɪtə floʊ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linked List Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos de lista enlazada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lɪŋkt lɪst ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A linked list is a fundamental data structure in computer science.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una lista enlazada es una estructura de datos fundamental en la informática.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə lɪŋkt lɪst ɪz ə ˌfʌndəˈmɛntəl ˈdeɪtə ˈstrʌkʧər ɪn kəmˈpjutər ˈsaɪəns.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">It mainly allows efficient insertion and deletion operations compared to arrays.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principalmente, permite operaciones de inserción y eliminación eficientes en comparación con las matrices.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɪt ˈmeɪnli əˈlaʊz ɪˈfɪʃənt ɪnˈsɜrʃən ænd dɪˈliʃən ˌɑpəˈreɪʃənz kəmˈpɛrd tu əˈreɪz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Like arrays, it is also used to implement other data structures like stack, queue and deque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al igual que las matrices, también se utiliza para implementar otras estructuras de datos como pila, cola y deque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laɪk əˈreɪz, ɪt ɪz ˈɔlsoʊ juzd tu ˈɪmpləˌmɛnt ˈʌðər ˈdeɪtə ˈstrʌkʧərz laɪk stæk, kju ænd deque.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Here’s the comparison of Linked List vs Arrays</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A continuación, se muestra la comparación de lista enlazada frente a matrices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hɪrz ðə kəmˈpɛrəsən ʌv lɪŋkt lɪst ˈvɜrsəz əˈreɪz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashing in Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hash en la estructura de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈhæʃɪŋ ɪn ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashing is a technique used in data structures that efficiently stores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El hash es una técnica utilizada en estructuras de datos que almacena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈhæʃɪŋ ɪz ə tɛkˈnik juzd ɪn ˈdeɪtə ˈstrʌkʧərz ðæt ɪˈfɪʃəntli stɔrz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and retrieves data in a way that allows for quick access.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y recupera datos de manera eficiente de una manera que permite un acceso rápido.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ænd rɪˈtrivz ˈdeɪtə ɪn ə weɪ ðæt əˈlaʊz fɔr kwɪk ˈækˌsɛs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashing involves mapping data to a specific index in a hash table (an array of items) -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El hash implica asignar datos a un índice específico en una tabla hash (una matriz de elementos) -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈhæʃɪŋ ɪnˈvɑlvz ˈmæpɪŋ ˈdeɪtə tu ə spəˈsɪfɪk ˈɪndɛks ɪn ə hæʃ ˈteɪbəl (ən əˈreɪ ʌv ˈaɪtəmz) -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- using a hash function that enables fast retrieval of information based on its key.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- utilizando una función hash que permite la recuperación rápida de información en función de su clave.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ˈjuzɪŋ ə hæʃ ˈfʌŋkʃən ðæt ɛˈneɪbəlz fæst rɪˈtrivəl ʌv ˌɪnfərˈmeɪʃən beɪst ɑn ɪts ki.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The great thing about hashing is,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo bueno del hash es que</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ðə ɡreɪt θɪŋ əˈbaʊt ˈhæʃɪŋ ɪz,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">we can achieve all three operations (search, insert and delete) in O(1) time on average.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">podemos lograr las tres operaciones (búsqueda, inserción y eliminación) en un tiempo O(1) en promedio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">wi kæn əˈʧiv ɔl θri ˌɑpəˈreɪʃənz (sɜrʧ, ɪnˈsɜrt ænd dɪˈlit) ɪn oʊ(1) taɪm ɑn ˈævərɪʤ.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashing is mainly used to implement a set of distinct items</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El hash se utiliza principalmente para implementar un conjunto de elementos distintos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈhæʃɪŋ ɪz ˈmeɪnli juzd tu ˈɪmpləˌmɛnt ə sɛt ʌv dɪˈstɪŋkt ˈaɪtəmz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">and dictionaries (key value pairs).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">y diccionarios (pares clave-valor).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ænd ˈdɪkʃəˌnɛriz (ki ˈvælju pɛrz).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos en forma de árbol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tri ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tree Data Structure is a non-linear data structure in which a collection of -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La estructura de datos en forma de árbol es una estructura de datos no lineal en la que una colección de</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tri ˈdeɪtə ˈstrʌkʧər ɪz ə nɑnˈlɪˌniər ˈdeɪtə ˈstrʌkʧər ɪn wɪʧ ə kəˈlɛkʃən ʌv -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- elements known as nodes are connected to each other via edges such that -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">elementos, conocidos como nodos, están conectados entre sí a través de aristas de modo que</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ˈɛləmənts noʊn æz noʊdz ɑr kəˈnɛktɪd tu iʧ ˈʌðər ˈvaɪə ˈɛʤəz sʌʧ ðæt -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- there exists exactly one path between any two nodes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">existe exactamente una ruta entre dos nodos cualesquiera.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">- ðɛr ɪɡˈzɪsts ɪɡˈzæktli wʌn pæθ bɪˈtwin ˈɛni tu noʊdz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Binary Tree Data Structure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura de datos de árbol binario</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ˈbaɪnəri tri ˈdeɪtə ˈstrʌkʧər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A Binary Tree Data Structure is a hierarchical data structure -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una estructura de datos de árbol binario es una estructura de datos jerárquica -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ə ˈbaɪnəri tri ˈdeɪtə ˈstrʌkʧər ɪz ə ˌhaɪˈrɑrkəkəl ˈdeɪtə ˈstrʌkʧər -</t>
   </si>
   <si>
     <t xml:space="preserve">- in which each node has at most two children,</t>
@@ -2568,7 +2586,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2589,6 +2607,17 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val=""/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2633,13 +2662,17 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2660,14 +2693,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4686480</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>2383560</xdr:rowOff>
+      <xdr:colOff>4686120</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2383200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2680,8 +2713,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29227320" y="1788120"/>
-          <a:ext cx="4686480" cy="2383560"/>
+          <a:off x="29227320" y="2084760"/>
+          <a:ext cx="4686120" cy="2383200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2698,14 +2731,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843080</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>2343240</xdr:rowOff>
+      <xdr:colOff>4842720</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>2342880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2718,8 +2751,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29227320" y="12969720"/>
-          <a:ext cx="4843080" cy="2343240"/>
+          <a:off x="29227320" y="14428440"/>
+          <a:ext cx="4842720" cy="2342880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2736,14 +2769,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4825080</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>2332800</xdr:rowOff>
+      <xdr:colOff>4824720</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>2332440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2756,8 +2789,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29227320" y="16629840"/>
-          <a:ext cx="4825080" cy="2332800"/>
+          <a:off x="29227320" y="16950600"/>
+          <a:ext cx="4824720" cy="2332440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2774,14 +2807,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4782240</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>2313720</xdr:rowOff>
+      <xdr:colOff>4781880</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>2313360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2794,8 +2827,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29227320" y="20969640"/>
-          <a:ext cx="4782240" cy="2313720"/>
+          <a:off x="29227320" y="20464200"/>
+          <a:ext cx="4781880" cy="2313360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2812,14 +2845,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>72000</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843440</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>2164680</xdr:rowOff>
+      <xdr:colOff>4843080</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2164320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2832,8 +2865,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29299320" y="24704640"/>
-          <a:ext cx="4771440" cy="2164680"/>
+          <a:off x="29299320" y="22898880"/>
+          <a:ext cx="4771080" cy="2164320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2860,9 +2893,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2895840</xdr:colOff>
+      <xdr:colOff>2895480</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2093040</xdr:rowOff>
+      <xdr:rowOff>2092680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2876,7 +2909,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="0"/>
-          <a:ext cx="2895840" cy="2093040"/>
+          <a:ext cx="2895480" cy="2092680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2898,9 +2931,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4588920</xdr:colOff>
+      <xdr:colOff>4588560</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>2412360</xdr:rowOff>
+      <xdr:rowOff>2412000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2914,7 +2947,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="3029040"/>
-          <a:ext cx="4588920" cy="2412360"/>
+          <a:ext cx="4588560" cy="2412000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2936,9 +2969,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4619160</xdr:colOff>
+      <xdr:colOff>4618800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2227320</xdr:rowOff>
+      <xdr:rowOff>2226960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2952,7 +2985,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="6878160"/>
-          <a:ext cx="4619160" cy="2227320"/>
+          <a:ext cx="4618800" cy="2226960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2979,9 +3012,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4753800</xdr:colOff>
+      <xdr:colOff>4753440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2163960</xdr:rowOff>
+      <xdr:rowOff>2163600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2995,7 +3028,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="0"/>
-          <a:ext cx="4753800" cy="2163960"/>
+          <a:ext cx="4753440" cy="2163600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3017,9 +3050,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2388960</xdr:colOff>
+      <xdr:colOff>2388600</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2617920</xdr:rowOff>
+      <xdr:rowOff>2617560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3033,7 +3066,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="9611280"/>
-          <a:ext cx="2388960" cy="2617920"/>
+          <a:ext cx="2388600" cy="2617560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3055,9 +3088,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1827000</xdr:colOff>
+      <xdr:colOff>1826640</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>2122560</xdr:rowOff>
+      <xdr:rowOff>2122200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3071,7 +3104,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="12677040"/>
-          <a:ext cx="1827000" cy="2122560"/>
+          <a:ext cx="1826640" cy="2122200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3093,9 +3126,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2341440</xdr:colOff>
+      <xdr:colOff>2341080</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2646360</xdr:rowOff>
+      <xdr:rowOff>2646000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3109,7 +3142,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="15085080"/>
-          <a:ext cx="2341440" cy="2646360"/>
+          <a:ext cx="2341080" cy="2646000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3131,9 +3164,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2074680</xdr:colOff>
+      <xdr:colOff>2074320</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>2494080</xdr:rowOff>
+      <xdr:rowOff>2493720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3147,7 +3180,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="18180000"/>
-          <a:ext cx="2074680" cy="2494080"/>
+          <a:ext cx="2074320" cy="2493720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3169,9 +3202,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2779560</xdr:colOff>
+      <xdr:colOff>2779200</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1769760</xdr:rowOff>
+      <xdr:rowOff>1769400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3185,7 +3218,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="4785480"/>
-          <a:ext cx="2779560" cy="1769760"/>
+          <a:ext cx="2779200" cy="1769400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3207,9 +3240,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2189160</xdr:colOff>
+      <xdr:colOff>2188800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1541160</xdr:rowOff>
+      <xdr:rowOff>1540800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3223,7 +3256,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="7211520"/>
-          <a:ext cx="2189160" cy="1541160"/>
+          <a:ext cx="2188800" cy="1540800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3245,9 +3278,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2303280</xdr:colOff>
+      <xdr:colOff>2302920</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>2598840</xdr:rowOff>
+      <xdr:rowOff>2598480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3261,7 +3294,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="21173400"/>
-          <a:ext cx="2303280" cy="2598840"/>
+          <a:ext cx="2302920" cy="2598480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3283,9 +3316,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2351160</xdr:colOff>
+      <xdr:colOff>2350800</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>2465280</xdr:rowOff>
+      <xdr:rowOff>2464920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3299,7 +3332,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="24076800"/>
-          <a:ext cx="2351160" cy="2465280"/>
+          <a:ext cx="2350800" cy="2464920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3321,9 +3354,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2141280</xdr:colOff>
+      <xdr:colOff>2140920</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>2465280</xdr:rowOff>
+      <xdr:rowOff>2464920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3337,7 +3370,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="26878320"/>
-          <a:ext cx="2141280" cy="2465280"/>
+          <a:ext cx="2140920" cy="2464920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3359,9 +3392,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112840</xdr:colOff>
+      <xdr:colOff>2112480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>2455920</xdr:rowOff>
+      <xdr:rowOff>2455560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3375,7 +3408,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="29679840"/>
-          <a:ext cx="2112840" cy="2455920"/>
+          <a:ext cx="2112480" cy="2455560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3397,9 +3430,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112840</xdr:colOff>
+      <xdr:colOff>2112480</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>2522520</xdr:rowOff>
+      <xdr:rowOff>2522160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3413,7 +3446,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="32496120"/>
-          <a:ext cx="2112840" cy="2522520"/>
+          <a:ext cx="2112480" cy="2522160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3435,9 +3468,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1998720</xdr:colOff>
+      <xdr:colOff>1998360</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>2370240</xdr:rowOff>
+      <xdr:rowOff>2369880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3451,7 +3484,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="35517960"/>
-          <a:ext cx="1998720" cy="2370240"/>
+          <a:ext cx="1998360" cy="2369880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3473,9 +3506,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2475000</xdr:colOff>
+      <xdr:colOff>2474640</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>2550960</xdr:rowOff>
+      <xdr:rowOff>2550600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3489,7 +3522,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="38261160"/>
-          <a:ext cx="2475000" cy="2550960"/>
+          <a:ext cx="2474640" cy="2550600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3511,9 +3544,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1941480</xdr:colOff>
+      <xdr:colOff>1941120</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2570040</xdr:rowOff>
+      <xdr:rowOff>2569680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3527,7 +3560,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="41193720"/>
-          <a:ext cx="1941480" cy="2570040"/>
+          <a:ext cx="1941120" cy="2569680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3549,9 +3582,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4662360</xdr:colOff>
+      <xdr:colOff>4662000</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>2762640</xdr:rowOff>
+      <xdr:rowOff>2762280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3565,7 +3598,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="45722520"/>
-          <a:ext cx="4662360" cy="2762640"/>
+          <a:ext cx="4662000" cy="2762280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3587,9 +3620,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3722760</xdr:colOff>
+      <xdr:colOff>3722400</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1817640</xdr:rowOff>
+      <xdr:rowOff>1817280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,7 +3636,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="49140720"/>
-          <a:ext cx="3722760" cy="1817640"/>
+          <a:ext cx="3722400" cy="1817280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3625,9 +3658,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4766040</xdr:colOff>
+      <xdr:colOff>4765680</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>2831760</xdr:rowOff>
+      <xdr:rowOff>2831400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3641,7 +3674,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="51640200"/>
-          <a:ext cx="4766040" cy="2831760"/>
+          <a:ext cx="4765680" cy="2831400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3663,9 +3696,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4708800</xdr:colOff>
+      <xdr:colOff>4708440</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>2797560</xdr:rowOff>
+      <xdr:rowOff>2797200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,7 +3712,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="55145880"/>
-          <a:ext cx="4708800" cy="2797560"/>
+          <a:ext cx="4708440" cy="2797200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3806,7 +3839,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="105.94"/>
@@ -3815,1308 +3848,236 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="69.56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="50.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="113.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="202.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="50.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="37.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="37.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="50.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="50.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="202.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="1" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="1" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="63.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="1" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="101" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="1" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="198.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="200.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="1" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="75.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="1" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="191.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="1" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="183.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="198.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="200.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="191.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="183.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5147,259 +4108,259 @@
   <sheetData>
     <row r="1" customFormat="false" ht="174.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>297</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>298</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>299</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>300</v>
+        <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>302</v>
+        <v>71</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>303</v>
+        <v>72</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>73</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>74</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>307</v>
+        <v>76</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>311</v>
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>312</v>
+        <v>81</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="213.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>315</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>316</v>
+        <v>85</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>317</v>
+        <v>86</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>318</v>
+        <v>87</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>319</v>
+        <v>88</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>320</v>
+        <v>89</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>321</v>
+        <v>90</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>322</v>
+        <v>91</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>323</v>
+        <v>92</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>324</v>
+        <v>93</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>325</v>
+        <v>94</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>326</v>
+        <v>95</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>327</v>
+        <v>96</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>328</v>
+        <v>97</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>329</v>
+        <v>98</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>330</v>
+        <v>99</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>331</v>
+        <v>100</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>332</v>
+        <v>101</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>334</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>335</v>
+        <v>104</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>336</v>
+        <v>105</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="185.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>337</v>
+        <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>339</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>340</v>
+        <v>109</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>341</v>
+        <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>342</v>
+        <v>111</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>343</v>
+        <v>112</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>344</v>
+        <v>113</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>345</v>
+        <v>114</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>346</v>
+        <v>115</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>347</v>
+        <v>116</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>348</v>
+        <v>117</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>349</v>
+        <v>118</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>350</v>
+        <v>119</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>351</v>
+        <v>120</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -5430,1677 +4391,1677 @@
   <sheetData>
     <row r="1" customFormat="false" ht="184.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>353</v>
+        <v>122</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>354</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>355</v>
+        <v>124</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>356</v>
+        <v>125</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>357</v>
+        <v>126</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>359</v>
+        <v>128</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>360</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>130</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>131</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>132</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>364</v>
+        <v>133</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>365</v>
+        <v>134</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>366</v>
+        <v>135</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>367</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>369</v>
+        <v>138</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>370</v>
+        <v>139</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>371</v>
+        <v>140</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>372</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>374</v>
+        <v>143</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>375</v>
+        <v>144</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>376</v>
+        <v>145</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>377</v>
+        <v>146</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>378</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>379</v>
+        <v>148</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>380</v>
+        <v>149</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>381</v>
+        <v>150</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>382</v>
+        <v>151</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>383</v>
+        <v>152</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>384</v>
+        <v>153</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>385</v>
+        <v>154</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>386</v>
+        <v>155</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>387</v>
+        <v>156</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>388</v>
+        <v>157</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>389</v>
+        <v>158</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>390</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>391</v>
+        <v>160</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>392</v>
+        <v>161</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>393</v>
+        <v>162</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>394</v>
+        <v>163</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>395</v>
+        <v>164</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>396</v>
+        <v>165</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>397</v>
+        <v>166</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>398</v>
+        <v>167</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>399</v>
+        <v>168</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="152.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>400</v>
+        <v>169</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>401</v>
+        <v>170</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>402</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>403</v>
+        <v>172</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>404</v>
+        <v>173</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>405</v>
+        <v>174</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>406</v>
+        <v>175</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>407</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>408</v>
+        <v>177</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>409</v>
+        <v>178</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>410</v>
+        <v>179</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>411</v>
+        <v>180</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="137.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>412</v>
+        <v>181</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>413</v>
+        <v>182</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>414</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>415</v>
+        <v>184</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>416</v>
+        <v>185</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>417</v>
+        <v>186</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>418</v>
+        <v>187</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>419</v>
+        <v>188</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>420</v>
+        <v>189</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>421</v>
+        <v>190</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>422</v>
+        <v>191</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>423</v>
+        <v>192</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>424</v>
+        <v>193</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>425</v>
+        <v>194</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>426</v>
+        <v>195</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>427</v>
+        <v>196</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>428</v>
+        <v>197</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>429</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>430</v>
+        <v>199</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>431</v>
+        <v>200</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>432</v>
+        <v>201</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>433</v>
+        <v>202</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>434</v>
+        <v>203</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>435</v>
+        <v>204</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="176.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>436</v>
+        <v>205</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>437</v>
+        <v>206</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>438</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>439</v>
+        <v>208</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>440</v>
+        <v>209</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>441</v>
+        <v>210</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>442</v>
+        <v>211</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>443</v>
+        <v>212</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>444</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>445</v>
+        <v>214</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>446</v>
+        <v>215</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>447</v>
+        <v>216</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>448</v>
+        <v>217</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>449</v>
+        <v>218</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>450</v>
+        <v>219</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="210.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>451</v>
+        <v>220</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>452</v>
+        <v>221</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>453</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>454</v>
+        <v>223</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>455</v>
+        <v>224</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>456</v>
+        <v>225</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>457</v>
+        <v>226</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>458</v>
+        <v>227</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>459</v>
+        <v>228</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>460</v>
+        <v>229</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>461</v>
+        <v>230</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>462</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>463</v>
+        <v>232</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>464</v>
+        <v>233</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>465</v>
+        <v>234</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="207.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>466</v>
+        <v>235</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>467</v>
+        <v>236</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>468</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>469</v>
+        <v>238</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>470</v>
+        <v>239</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>471</v>
+        <v>240</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="207.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>472</v>
+        <v>241</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>473</v>
+        <v>242</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>474</v>
+        <v>243</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>475</v>
+        <v>244</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>476</v>
+        <v>245</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>477</v>
+        <v>246</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="208.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>478</v>
+        <v>247</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>479</v>
+        <v>248</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>480</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>481</v>
+        <v>250</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>482</v>
+        <v>251</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>483</v>
+        <v>252</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="212.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>484</v>
+        <v>253</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>485</v>
+        <v>254</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>486</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>487</v>
+        <v>256</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>488</v>
+        <v>257</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>489</v>
+        <v>258</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>490</v>
+        <v>259</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>491</v>
+        <v>260</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>492</v>
+        <v>261</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="203.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>493</v>
+        <v>262</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>494</v>
+        <v>263</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>495</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>496</v>
+        <v>265</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>497</v>
+        <v>266</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>498</v>
+        <v>267</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>499</v>
+        <v>268</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>500</v>
+        <v>269</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>501</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>502</v>
+        <v>271</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>503</v>
+        <v>272</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>504</v>
+        <v>273</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="215.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>505</v>
+        <v>274</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>506</v>
+        <v>275</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>507</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>508</v>
+        <v>277</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>509</v>
+        <v>278</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>510</v>
+        <v>279</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>511</v>
+        <v>280</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>512</v>
+        <v>281</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>513</v>
+        <v>282</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>514</v>
+        <v>283</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>515</v>
+        <v>284</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>516</v>
+        <v>285</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>517</v>
+        <v>286</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>518</v>
+        <v>287</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>519</v>
+        <v>288</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>520</v>
+        <v>289</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>521</v>
+        <v>290</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>522</v>
+        <v>291</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>523</v>
+        <v>292</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>524</v>
+        <v>293</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>525</v>
+        <v>294</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>526</v>
+        <v>295</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>527</v>
+        <v>296</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>528</v>
+        <v>297</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>529</v>
+        <v>298</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>530</v>
+        <v>299</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>531</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>532</v>
+        <v>301</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>533</v>
+        <v>302</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>534</v>
+        <v>303</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>535</v>
+        <v>304</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>536</v>
+        <v>305</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>537</v>
+        <v>306</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>538</v>
+        <v>307</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>539</v>
+        <v>308</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>540</v>
+        <v>309</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="230.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>541</v>
+        <v>310</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>542</v>
+        <v>311</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>543</v>
+        <v>312</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>544</v>
+        <v>313</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>545</v>
+        <v>314</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>546</v>
+        <v>315</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>547</v>
+        <v>316</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>548</v>
+        <v>317</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>549</v>
+        <v>318</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>550</v>
+        <v>319</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>551</v>
+        <v>320</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>552</v>
+        <v>321</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="158.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>553</v>
+        <v>322</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>554</v>
+        <v>323</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>555</v>
+        <v>324</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>556</v>
+        <v>325</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>557</v>
+        <v>326</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>558</v>
+        <v>327</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>559</v>
+        <v>328</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>560</v>
+        <v>329</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>561</v>
+        <v>330</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>562</v>
+        <v>331</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>563</v>
+        <v>332</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>564</v>
+        <v>333</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="237.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>565</v>
+        <v>334</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>566</v>
+        <v>335</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>567</v>
+        <v>336</v>
       </c>
       <c r="F72" s="1"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>568</v>
+        <v>337</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>569</v>
+        <v>338</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>570</v>
+        <v>339</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>571</v>
+        <v>340</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>572</v>
+        <v>341</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>573</v>
+        <v>342</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>574</v>
+        <v>343</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>575</v>
+        <v>344</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>576</v>
+        <v>345</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="234.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>577</v>
+        <v>346</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>578</v>
+        <v>347</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>579</v>
+        <v>348</v>
       </c>
       <c r="F76" s="1"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>580</v>
+        <v>349</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>581</v>
+        <v>350</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>582</v>
+        <v>351</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>583</v>
+        <v>352</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>584</v>
+        <v>353</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>585</v>
+        <v>354</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>586</v>
+        <v>355</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>587</v>
+        <v>356</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>588</v>
+        <v>357</v>
       </c>
       <c r="F79" s="1"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>589</v>
+        <v>358</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>590</v>
+        <v>359</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>591</v>
+        <v>360</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>592</v>
+        <v>361</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>593</v>
+        <v>362</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>594</v>
+        <v>363</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>595</v>
+        <v>364</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>596</v>
+        <v>365</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>597</v>
+        <v>366</v>
       </c>
       <c r="F82" s="1"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>598</v>
+        <v>367</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>599</v>
+        <v>368</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>600</v>
+        <v>369</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>601</v>
+        <v>370</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>602</v>
+        <v>371</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>603</v>
+        <v>372</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>604</v>
+        <v>373</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>605</v>
+        <v>374</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>606</v>
+        <v>375</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>607</v>
+        <v>376</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>608</v>
+        <v>377</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>609</v>
+        <v>378</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>610</v>
+        <v>379</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>611</v>
+        <v>380</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>612</v>
+        <v>381</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>613</v>
+        <v>382</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>614</v>
+        <v>383</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>615</v>
+        <v>384</v>
       </c>
       <c r="F88" s="1"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>616</v>
+        <v>385</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>617</v>
+        <v>386</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>618</v>
+        <v>387</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>619</v>
+        <v>388</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>620</v>
+        <v>389</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>621</v>
+        <v>390</v>
       </c>
       <c r="F90" s="1"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>622</v>
+        <v>391</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>623</v>
+        <v>392</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>624</v>
+        <v>393</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>625</v>
+        <v>394</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>626</v>
+        <v>395</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>627</v>
+        <v>396</v>
       </c>
       <c r="F92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>628</v>
+        <v>397</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>629</v>
+        <v>398</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>630</v>
+        <v>399</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>631</v>
+        <v>400</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>632</v>
+        <v>401</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>633</v>
+        <v>402</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>634</v>
+        <v>403</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>635</v>
+        <v>404</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>636</v>
+        <v>405</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>637</v>
+        <v>406</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>638</v>
+        <v>407</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>639</v>
+        <v>408</v>
       </c>
       <c r="F96" s="1"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>640</v>
+        <v>409</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>641</v>
+        <v>410</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>642</v>
+        <v>411</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>643</v>
+        <v>412</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>644</v>
+        <v>413</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>645</v>
+        <v>414</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>646</v>
+        <v>415</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>647</v>
+        <v>416</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>648</v>
+        <v>417</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>649</v>
+        <v>418</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>650</v>
+        <v>419</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>651</v>
+        <v>420</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>652</v>
+        <v>421</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>653</v>
+        <v>422</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>654</v>
+        <v>423</v>
       </c>
       <c r="F101" s="1"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>655</v>
+        <v>424</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>656</v>
+        <v>425</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>657</v>
+        <v>426</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>658</v>
+        <v>427</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>659</v>
+        <v>428</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>660</v>
+        <v>429</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>661</v>
+        <v>430</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>662</v>
+        <v>431</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>663</v>
+        <v>432</v>
       </c>
       <c r="F104" s="1"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>664</v>
+        <v>433</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>665</v>
+        <v>434</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>666</v>
+        <v>435</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>667</v>
+        <v>436</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>668</v>
+        <v>437</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>669</v>
+        <v>438</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>670</v>
+        <v>439</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>671</v>
+        <v>440</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>672</v>
+        <v>441</v>
       </c>
       <c r="F107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>673</v>
+        <v>442</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>674</v>
+        <v>443</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>675</v>
+        <v>444</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>676</v>
+        <v>445</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>677</v>
+        <v>446</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>678</v>
+        <v>447</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>679</v>
+        <v>448</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>680</v>
+        <v>449</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>681</v>
+        <v>450</v>
       </c>
       <c r="F110" s="1"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>682</v>
+        <v>451</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>683</v>
+        <v>452</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>684</v>
+        <v>453</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>685</v>
+        <v>454</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>686</v>
+        <v>455</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>687</v>
+        <v>456</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>688</v>
+        <v>457</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>689</v>
+        <v>458</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>690</v>
+        <v>459</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>691</v>
+        <v>460</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>692</v>
+        <v>461</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>693</v>
+        <v>462</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
-        <v>694</v>
+        <v>463</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>695</v>
+        <v>464</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>696</v>
+        <v>465</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
-        <v>697</v>
+        <v>466</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>698</v>
+        <v>467</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>699</v>
+        <v>468</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>700</v>
+        <v>469</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>701</v>
+        <v>470</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>702</v>
+        <v>471</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
-        <v>703</v>
+        <v>472</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>704</v>
+        <v>473</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>705</v>
+        <v>474</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
-        <v>706</v>
+        <v>475</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>707</v>
+        <v>476</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>708</v>
+        <v>477</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
-        <v>709</v>
+        <v>478</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>710</v>
+        <v>479</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>711</v>
+        <v>480</v>
       </c>
       <c r="F120" s="1"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
-        <v>712</v>
+        <v>481</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>713</v>
+        <v>482</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>714</v>
+        <v>483</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
-        <v>715</v>
+        <v>484</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>716</v>
+        <v>485</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>717</v>
+        <v>486</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
-        <v>718</v>
+        <v>487</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>719</v>
+        <v>488</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>720</v>
+        <v>489</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
-        <v>721</v>
+        <v>490</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>722</v>
+        <v>491</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>723</v>
+        <v>492</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
-        <v>724</v>
+        <v>493</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>725</v>
+        <v>494</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>726</v>
+        <v>495</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
-        <v>727</v>
+        <v>496</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>728</v>
+        <v>497</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>729</v>
+        <v>498</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -7130,504 +6091,504 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>730</v>
+        <v>499</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>731</v>
+        <v>500</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>732</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>733</v>
+        <v>502</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>734</v>
+        <v>503</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>735</v>
+        <v>504</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>736</v>
+        <v>505</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>737</v>
+        <v>506</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>738</v>
+        <v>507</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>739</v>
+        <v>508</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>740</v>
+        <v>509</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>741</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>742</v>
+        <v>511</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>743</v>
+        <v>512</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>744</v>
+        <v>513</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>745</v>
+        <v>514</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>746</v>
+        <v>515</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>747</v>
+        <v>516</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>748</v>
+        <v>517</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>749</v>
+        <v>518</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>750</v>
+        <v>519</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>751</v>
+        <v>520</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>752</v>
+        <v>521</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>753</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>754</v>
+        <v>523</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>755</v>
+        <v>524</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>756</v>
+        <v>525</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>757</v>
+        <v>526</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>758</v>
+        <v>527</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>759</v>
+        <v>528</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>760</v>
+        <v>529</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>761</v>
+        <v>530</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>762</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>763</v>
+        <v>532</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>764</v>
+        <v>533</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>765</v>
+        <v>534</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>766</v>
+        <v>535</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>767</v>
+        <v>536</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>768</v>
+        <v>537</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>769</v>
+        <v>538</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>770</v>
+        <v>539</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>771</v>
+        <v>540</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>772</v>
+        <v>541</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>773</v>
+        <v>542</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>774</v>
+        <v>543</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>775</v>
+        <v>544</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>776</v>
+        <v>545</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>777</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>778</v>
+        <v>547</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>779</v>
+        <v>548</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>780</v>
+        <v>549</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>781</v>
+        <v>550</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>782</v>
+        <v>551</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>783</v>
+        <v>552</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>784</v>
+        <v>553</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>785</v>
+        <v>554</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>786</v>
+        <v>555</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>787</v>
+        <v>556</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>788</v>
+        <v>557</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>789</v>
+        <v>558</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>790</v>
+        <v>559</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>791</v>
+        <v>560</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>792</v>
+        <v>561</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>793</v>
+        <v>562</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>794</v>
+        <v>563</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>795</v>
+        <v>564</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>796</v>
+        <v>565</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>797</v>
+        <v>566</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>798</v>
+        <v>567</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>799</v>
+        <v>568</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>800</v>
+        <v>569</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>801</v>
+        <v>570</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>802</v>
+        <v>571</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>803</v>
+        <v>572</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>804</v>
+        <v>573</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>805</v>
+        <v>574</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>806</v>
+        <v>575</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>807</v>
+        <v>576</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>808</v>
+        <v>577</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>809</v>
+        <v>578</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>810</v>
+        <v>579</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>811</v>
+        <v>580</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>812</v>
+        <v>581</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>813</v>
+        <v>582</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>814</v>
+        <v>583</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>815</v>
+        <v>584</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>816</v>
+        <v>585</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>817</v>
+        <v>586</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>818</v>
+        <v>587</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>819</v>
+        <v>588</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>820</v>
+        <v>589</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>821</v>
+        <v>590</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>822</v>
+        <v>591</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>823</v>
+        <v>592</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>824</v>
+        <v>593</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>825</v>
+        <v>594</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>826</v>
+        <v>595</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>827</v>
+        <v>596</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>828</v>
+        <v>597</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>829</v>
+        <v>598</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>830</v>
+        <v>599</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>831</v>
+        <v>600</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>832</v>
+        <v>601</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>833</v>
+        <v>602</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>834</v>
+        <v>603</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>835</v>
+        <v>604</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>836</v>
+        <v>605</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>837</v>
+        <v>606</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>838</v>
+        <v>607</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>839</v>
+        <v>608</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>840</v>
+        <v>609</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>841</v>
+        <v>610</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>842</v>
+        <v>611</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>843</v>
+        <v>612</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -7654,7 +6615,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>844</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
+++ b/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="1 Algoritms" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="845">
   <si>
     <t xml:space="preserve">Data structures are the fundamental building blocks of computer programming.</t>
   </si>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">ɪɡˈzæmpəlz: triz ænd ɡræfs.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Array:</t>
+    <t xml:space="preserve">Array:</t>
   </si>
   <si>
     <t xml:space="preserve">1. Matriz:</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">- ˈʌðər ˈdeɪtə ˈstrʌkʧərz laɪk stæk kju, Deque, ɡræf, hæʃ ˈteɪbəl, ˌɛtˈsɛtərə.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Matrix/Grid</t>
+    <t xml:space="preserve">Matrix/Grid</t>
   </si>
   <si>
     <t xml:space="preserve">2. Matriz/Cuadrícula</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">ˈmeɪtrɪsɪz əˈlaʊ fɔr ɪˈfɪʃənt ˈstɔrəʤ ænd məˌnɪpjəˈleɪʃən ʌv ˈdeɪtə ɪn ə ˈstrʌkʧərd ˈfɔrˌmæt.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. String</t>
+    <t xml:space="preserve">String</t>
   </si>
   <si>
     <t xml:space="preserve">3. Cadena</t>
@@ -2665,9 +2665,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4686480</xdr:colOff>
+      <xdr:colOff>4686120</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2383560</xdr:rowOff>
+      <xdr:rowOff>2383200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2681,7 +2681,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="1788120"/>
-          <a:ext cx="4686480" cy="2383560"/>
+          <a:ext cx="4686120" cy="2383200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2703,9 +2703,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843080</xdr:colOff>
+      <xdr:colOff>4842720</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>2343240</xdr:rowOff>
+      <xdr:rowOff>2342880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2719,7 +2719,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="12969720"/>
-          <a:ext cx="4843080" cy="2343240"/>
+          <a:ext cx="4842720" cy="2342880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2741,9 +2741,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4825080</xdr:colOff>
+      <xdr:colOff>4824720</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>2332800</xdr:rowOff>
+      <xdr:rowOff>2332440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2757,7 +2757,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="16629840"/>
-          <a:ext cx="4825080" cy="2332800"/>
+          <a:ext cx="4824720" cy="2332440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2779,9 +2779,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4782240</xdr:colOff>
+      <xdr:colOff>4781880</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>2313720</xdr:rowOff>
+      <xdr:rowOff>2313360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2795,7 +2795,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="20969640"/>
-          <a:ext cx="4782240" cy="2313720"/>
+          <a:ext cx="4781880" cy="2313360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2817,9 +2817,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843440</xdr:colOff>
+      <xdr:colOff>4843080</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>2164680</xdr:rowOff>
+      <xdr:rowOff>2164320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2833,7 +2833,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29299320" y="24704640"/>
-          <a:ext cx="4771440" cy="2164680"/>
+          <a:ext cx="4771080" cy="2164320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2860,9 +2860,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2895840</xdr:colOff>
+      <xdr:colOff>2895480</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2093040</xdr:rowOff>
+      <xdr:rowOff>2092680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2876,7 +2876,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="0"/>
-          <a:ext cx="2895840" cy="2093040"/>
+          <a:ext cx="2895480" cy="2092680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2898,9 +2898,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4588920</xdr:colOff>
+      <xdr:colOff>4588560</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>2412360</xdr:rowOff>
+      <xdr:rowOff>2412000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2914,7 +2914,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="3029040"/>
-          <a:ext cx="4588920" cy="2412360"/>
+          <a:ext cx="4588560" cy="2412000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2936,9 +2936,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4619160</xdr:colOff>
+      <xdr:colOff>4618800</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2227320</xdr:rowOff>
+      <xdr:rowOff>2226960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2952,7 +2952,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="6878160"/>
-          <a:ext cx="4619160" cy="2227320"/>
+          <a:ext cx="4618800" cy="2226960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2979,9 +2979,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4753800</xdr:colOff>
+      <xdr:colOff>4753440</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2163960</xdr:rowOff>
+      <xdr:rowOff>2163600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2995,7 +2995,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="0"/>
-          <a:ext cx="4753800" cy="2163960"/>
+          <a:ext cx="4753440" cy="2163600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3017,9 +3017,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2388960</xdr:colOff>
+      <xdr:colOff>2388600</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2617920</xdr:rowOff>
+      <xdr:rowOff>2617560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3033,7 +3033,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="9611280"/>
-          <a:ext cx="2388960" cy="2617920"/>
+          <a:ext cx="2388600" cy="2617560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3055,9 +3055,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1827000</xdr:colOff>
+      <xdr:colOff>1826640</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>2122560</xdr:rowOff>
+      <xdr:rowOff>2122200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3071,7 +3071,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="12677040"/>
-          <a:ext cx="1827000" cy="2122560"/>
+          <a:ext cx="1826640" cy="2122200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3093,9 +3093,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2341440</xdr:colOff>
+      <xdr:colOff>2341080</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2646360</xdr:rowOff>
+      <xdr:rowOff>2646000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3109,7 +3109,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="15085080"/>
-          <a:ext cx="2341440" cy="2646360"/>
+          <a:ext cx="2341080" cy="2646000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3131,9 +3131,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2074680</xdr:colOff>
+      <xdr:colOff>2074320</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>2494080</xdr:rowOff>
+      <xdr:rowOff>2493720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3147,7 +3147,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="18180000"/>
-          <a:ext cx="2074680" cy="2494080"/>
+          <a:ext cx="2074320" cy="2493720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3169,9 +3169,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2779560</xdr:colOff>
+      <xdr:colOff>2779200</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1769760</xdr:rowOff>
+      <xdr:rowOff>1769400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3185,7 +3185,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="4785480"/>
-          <a:ext cx="2779560" cy="1769760"/>
+          <a:ext cx="2779200" cy="1769400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3207,9 +3207,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2189160</xdr:colOff>
+      <xdr:colOff>2188800</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1541160</xdr:rowOff>
+      <xdr:rowOff>1540800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3223,7 +3223,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="7211520"/>
-          <a:ext cx="2189160" cy="1541160"/>
+          <a:ext cx="2188800" cy="1540800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3245,9 +3245,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2303280</xdr:colOff>
+      <xdr:colOff>2302920</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>2598840</xdr:rowOff>
+      <xdr:rowOff>2598480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3261,7 +3261,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="21173400"/>
-          <a:ext cx="2303280" cy="2598840"/>
+          <a:ext cx="2302920" cy="2598480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3283,9 +3283,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2351160</xdr:colOff>
+      <xdr:colOff>2350800</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>2465280</xdr:rowOff>
+      <xdr:rowOff>2464920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3299,7 +3299,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="24076800"/>
-          <a:ext cx="2351160" cy="2465280"/>
+          <a:ext cx="2350800" cy="2464920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3321,9 +3321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2141280</xdr:colOff>
+      <xdr:colOff>2140920</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>2465280</xdr:rowOff>
+      <xdr:rowOff>2464920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3337,7 +3337,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="26878320"/>
-          <a:ext cx="2141280" cy="2465280"/>
+          <a:ext cx="2140920" cy="2464920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3359,9 +3359,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112840</xdr:colOff>
+      <xdr:colOff>2112480</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>2455920</xdr:rowOff>
+      <xdr:rowOff>2455560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3375,7 +3375,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="29679840"/>
-          <a:ext cx="2112840" cy="2455920"/>
+          <a:ext cx="2112480" cy="2455560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3397,9 +3397,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112840</xdr:colOff>
+      <xdr:colOff>2112480</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>2522520</xdr:rowOff>
+      <xdr:rowOff>2522160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3413,7 +3413,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="32496120"/>
-          <a:ext cx="2112840" cy="2522520"/>
+          <a:ext cx="2112480" cy="2522160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3435,9 +3435,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1998720</xdr:colOff>
+      <xdr:colOff>1998360</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>2370240</xdr:rowOff>
+      <xdr:rowOff>2369880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3451,7 +3451,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="35517960"/>
-          <a:ext cx="1998720" cy="2370240"/>
+          <a:ext cx="1998360" cy="2369880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3473,9 +3473,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2475000</xdr:colOff>
+      <xdr:colOff>2474640</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>2550960</xdr:rowOff>
+      <xdr:rowOff>2550600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3489,7 +3489,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="38261160"/>
-          <a:ext cx="2475000" cy="2550960"/>
+          <a:ext cx="2474640" cy="2550600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3511,9 +3511,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1941480</xdr:colOff>
+      <xdr:colOff>1941120</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2570040</xdr:rowOff>
+      <xdr:rowOff>2569680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3527,7 +3527,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="41193720"/>
-          <a:ext cx="1941480" cy="2570040"/>
+          <a:ext cx="1941120" cy="2569680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3549,9 +3549,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4662360</xdr:colOff>
+      <xdr:colOff>4662000</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>2762640</xdr:rowOff>
+      <xdr:rowOff>2762280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3565,7 +3565,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="45722520"/>
-          <a:ext cx="4662360" cy="2762640"/>
+          <a:ext cx="4662000" cy="2762280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3587,9 +3587,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3722760</xdr:colOff>
+      <xdr:colOff>3722400</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1817640</xdr:rowOff>
+      <xdr:rowOff>1817280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,7 +3603,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="49140720"/>
-          <a:ext cx="3722760" cy="1817640"/>
+          <a:ext cx="3722400" cy="1817280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3625,9 +3625,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4766040</xdr:colOff>
+      <xdr:colOff>4765680</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>2831760</xdr:rowOff>
+      <xdr:rowOff>2831400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3641,7 +3641,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="51640200"/>
-          <a:ext cx="4766040" cy="2831760"/>
+          <a:ext cx="4765680" cy="2831400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3663,9 +3663,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4708800</xdr:colOff>
+      <xdr:colOff>4708440</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>2797560</xdr:rowOff>
+      <xdr:rowOff>2797200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,7 +3679,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="55145880"/>
-          <a:ext cx="4708800" cy="2797560"/>
+          <a:ext cx="4708440" cy="2797200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3865,6 +3865,9 @@
       <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -3904,6 +3907,9 @@
       <c r="D7" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -3971,6 +3977,9 @@
       <c r="D12" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="F12" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -3982,6 +3991,9 @@
       <c r="D13" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -4049,6 +4061,9 @@
       <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -4088,6 +4103,9 @@
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -4141,6 +4159,9 @@
       <c r="D25" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -4247,6 +4268,9 @@
       <c r="D33" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
@@ -4272,6 +4296,9 @@
       <c r="D35" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="F35" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
@@ -4297,6 +4324,9 @@
       <c r="D37" s="1" t="s">
         <v>111</v>
       </c>
+      <c r="F37" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
@@ -4336,6 +4366,9 @@
       <c r="D40" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="F40" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
@@ -4375,6 +4408,9 @@
       <c r="D43" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -4428,6 +4464,9 @@
       <c r="D47" s="1" t="s">
         <v>141</v>
       </c>
+      <c r="F47" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
@@ -4481,6 +4520,9 @@
       <c r="D51" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="F51" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
@@ -4534,6 +4576,9 @@
       <c r="D55" s="1" t="s">
         <v>165</v>
       </c>
+      <c r="F55" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
@@ -4587,6 +4632,9 @@
       <c r="D59" s="1" t="s">
         <v>177</v>
       </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
@@ -4791,6 +4839,9 @@
       <c r="D74" s="1" t="s">
         <v>222</v>
       </c>
+      <c r="F74" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
@@ -4886,6 +4937,9 @@
       <c r="D81" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="F81" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
@@ -5075,6 +5129,9 @@
       </c>
       <c r="D95" s="1" t="s">
         <v>285</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5236,6 +5293,9 @@
       <c r="D7" s="1" t="s">
         <v>315</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -5344,6 +5404,9 @@
       </c>
       <c r="D15" s="1" t="s">
         <v>339</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5519,6 +5582,9 @@
       <c r="D7" s="1" t="s">
         <v>372</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -5600,6 +5666,9 @@
       <c r="D13" s="1" t="s">
         <v>390</v>
       </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -5653,6 +5722,9 @@
       <c r="D17" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="F17" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -5706,6 +5778,9 @@
       <c r="D21" s="1" t="s">
         <v>414</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -5773,6 +5848,9 @@
       <c r="D26" s="1" t="s">
         <v>429</v>
       </c>
+      <c r="F26" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
@@ -5812,6 +5890,9 @@
       <c r="D29" s="1" t="s">
         <v>438</v>
       </c>
+      <c r="F29" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -5837,6 +5918,9 @@
       <c r="D31" s="1" t="s">
         <v>444</v>
       </c>
+      <c r="F31" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
@@ -5940,6 +6024,9 @@
       <c r="D39" s="1" t="s">
         <v>468</v>
       </c>
+      <c r="F39" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
@@ -5990,6 +6077,9 @@
       <c r="D43" s="1" t="s">
         <v>480</v>
       </c>
+      <c r="F43" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -6015,6 +6105,9 @@
       <c r="D45" s="1" t="s">
         <v>486</v>
       </c>
+      <c r="F45" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
@@ -6054,6 +6147,9 @@
       <c r="D48" s="1" t="s">
         <v>495</v>
       </c>
+      <c r="F48" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
@@ -6079,6 +6175,9 @@
       <c r="D50" s="1" t="s">
         <v>501</v>
       </c>
+      <c r="F50" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
@@ -6104,6 +6203,9 @@
       <c r="D52" s="1" t="s">
         <v>507</v>
       </c>
+      <c r="F52" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
@@ -6143,6 +6245,9 @@
       <c r="D55" s="1" t="s">
         <v>516</v>
       </c>
+      <c r="F55" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
@@ -6210,6 +6315,9 @@
       <c r="D60" s="1" t="s">
         <v>531</v>
       </c>
+      <c r="F60" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
@@ -6316,6 +6424,9 @@
       <c r="D68" s="1" t="s">
         <v>555</v>
       </c>
+      <c r="F68" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
@@ -6369,7 +6480,9 @@
       <c r="D72" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F72" s="1"/>
+      <c r="F72" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
@@ -6463,7 +6576,9 @@
       <c r="D79" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="F79" s="1"/>
+      <c r="F79" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
@@ -6503,7 +6618,9 @@
       <c r="D82" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="F82" s="1"/>
+      <c r="F82" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
@@ -6585,7 +6702,9 @@
       <c r="D88" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="F88" s="1"/>
+      <c r="F88" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
@@ -6611,7 +6730,9 @@
       <c r="D90" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F90" s="1"/>
+      <c r="F90" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
@@ -6691,7 +6812,9 @@
       <c r="D96" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="F96" s="1"/>
+      <c r="F96" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
@@ -6759,7 +6882,9 @@
       <c r="D101" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="F101" s="1"/>
+      <c r="F101" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
@@ -6799,7 +6924,9 @@
       <c r="D104" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="F104" s="1"/>
+      <c r="F104" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
@@ -6839,7 +6966,9 @@
       <c r="D107" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="F107" s="1"/>
+      <c r="F107" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
@@ -6879,7 +7008,9 @@
       <c r="D110" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="F110" s="1"/>
+      <c r="F110" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
@@ -7017,7 +7148,9 @@
       <c r="D120" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F120" s="1"/>
+      <c r="F120" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
@@ -7177,6 +7310,9 @@
       <c r="D4" s="1" t="s">
         <v>741</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
@@ -7230,6 +7366,9 @@
       <c r="D8" s="1" t="s">
         <v>753</v>
       </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
@@ -7269,6 +7408,9 @@
       <c r="D11" s="1" t="s">
         <v>762</v>
       </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
@@ -7336,6 +7478,9 @@
       <c r="D16" s="1" t="s">
         <v>777</v>
       </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -7389,6 +7534,9 @@
       <c r="D20" s="1" t="s">
         <v>789</v>
       </c>
+      <c r="F20" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -7442,6 +7590,9 @@
       <c r="D24" s="1" t="s">
         <v>801</v>
       </c>
+      <c r="F24" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
@@ -7481,6 +7632,9 @@
       <c r="D27" s="1" t="s">
         <v>810</v>
       </c>
+      <c r="F27" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -7520,6 +7674,9 @@
       <c r="D30" s="1" t="s">
         <v>819</v>
       </c>
+      <c r="F30" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
@@ -7558,6 +7715,9 @@
       </c>
       <c r="D33" s="1" t="s">
         <v>828</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
+++ b/src/main/resources/espacios/Software/0 - Algoritmos y estructuras de datos.xlsx
@@ -2568,7 +2568,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2589,6 +2589,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2633,8 +2640,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2665,9 +2680,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4686120</xdr:colOff>
+      <xdr:colOff>4685760</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>2383200</xdr:rowOff>
+      <xdr:rowOff>2382840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2681,7 +2696,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="1788120"/>
-          <a:ext cx="4686120" cy="2383200"/>
+          <a:ext cx="4685760" cy="2382840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2703,9 +2718,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4842720</xdr:colOff>
+      <xdr:colOff>4842360</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>2342880</xdr:rowOff>
+      <xdr:rowOff>2342520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2719,7 +2734,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="12969720"/>
-          <a:ext cx="4842720" cy="2342880"/>
+          <a:ext cx="4842360" cy="2342520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2741,9 +2756,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4824720</xdr:colOff>
+      <xdr:colOff>4824360</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>2332440</xdr:rowOff>
+      <xdr:rowOff>2332080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2757,7 +2772,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="16629840"/>
-          <a:ext cx="4824720" cy="2332440"/>
+          <a:ext cx="4824360" cy="2332080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2779,9 +2794,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4781880</xdr:colOff>
+      <xdr:colOff>4781520</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>2313360</xdr:rowOff>
+      <xdr:rowOff>2313000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2795,7 +2810,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29227320" y="20969640"/>
-          <a:ext cx="4781880" cy="2313360"/>
+          <a:ext cx="4781520" cy="2313000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2817,9 +2832,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4843080</xdr:colOff>
+      <xdr:colOff>4842720</xdr:colOff>
       <xdr:row>94</xdr:row>
-      <xdr:rowOff>2164320</xdr:rowOff>
+      <xdr:rowOff>2163960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2833,7 +2848,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29299320" y="24704640"/>
-          <a:ext cx="4771080" cy="2164320"/>
+          <a:ext cx="4770720" cy="2163960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2860,9 +2875,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2895480</xdr:colOff>
+      <xdr:colOff>2895120</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2092680</xdr:rowOff>
+      <xdr:rowOff>2092320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2876,7 +2891,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="0"/>
-          <a:ext cx="2895480" cy="2092680"/>
+          <a:ext cx="2895120" cy="2092320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2898,9 +2913,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4588560</xdr:colOff>
+      <xdr:colOff>4588200</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>2412000</xdr:rowOff>
+      <xdr:rowOff>2411640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2914,7 +2929,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="3029040"/>
-          <a:ext cx="4588560" cy="2412000"/>
+          <a:ext cx="4588200" cy="2411640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2936,9 +2951,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4618800</xdr:colOff>
+      <xdr:colOff>4618440</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2226960</xdr:rowOff>
+      <xdr:rowOff>2226600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2952,7 +2967,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="22242960" y="6878160"/>
-          <a:ext cx="4618800" cy="2226960"/>
+          <a:ext cx="4618440" cy="2226600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2979,9 +2994,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4753440</xdr:colOff>
+      <xdr:colOff>4753080</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2163600</xdr:rowOff>
+      <xdr:rowOff>2163240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2995,7 +3010,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="0"/>
-          <a:ext cx="4753440" cy="2163600"/>
+          <a:ext cx="4753080" cy="2163240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3017,9 +3032,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2388600</xdr:colOff>
+      <xdr:colOff>2388240</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2617560</xdr:rowOff>
+      <xdr:rowOff>2617200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3033,7 +3048,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="9611280"/>
-          <a:ext cx="2388600" cy="2617560"/>
+          <a:ext cx="2388240" cy="2617200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3055,9 +3070,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1826640</xdr:colOff>
+      <xdr:colOff>1826280</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>2122200</xdr:rowOff>
+      <xdr:rowOff>2121840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3071,7 +3086,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="12677040"/>
-          <a:ext cx="1826640" cy="2122200"/>
+          <a:ext cx="1826280" cy="2121840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3093,9 +3108,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2341080</xdr:colOff>
+      <xdr:colOff>2340720</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2646000</xdr:rowOff>
+      <xdr:rowOff>2645640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3109,7 +3124,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="15085080"/>
-          <a:ext cx="2341080" cy="2646000"/>
+          <a:ext cx="2340720" cy="2645640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3131,9 +3146,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2074320</xdr:colOff>
+      <xdr:colOff>2073960</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>2493720</xdr:rowOff>
+      <xdr:rowOff>2493360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3147,7 +3162,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="18180000"/>
-          <a:ext cx="2074320" cy="2493720"/>
+          <a:ext cx="2073960" cy="2493360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3169,9 +3184,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2779200</xdr:colOff>
+      <xdr:colOff>2778840</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>1769400</xdr:rowOff>
+      <xdr:rowOff>1769040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3185,7 +3200,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="4785480"/>
-          <a:ext cx="2779200" cy="1769400"/>
+          <a:ext cx="2778840" cy="1769040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3207,9 +3222,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2188800</xdr:colOff>
+      <xdr:colOff>2188440</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1540800</xdr:rowOff>
+      <xdr:rowOff>1540440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3223,7 +3238,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="7211520"/>
-          <a:ext cx="2188800" cy="1540800"/>
+          <a:ext cx="2188440" cy="1540440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3245,9 +3260,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2302920</xdr:colOff>
+      <xdr:colOff>2302560</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>2598480</xdr:rowOff>
+      <xdr:rowOff>2598120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3261,7 +3276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="21173400"/>
-          <a:ext cx="2302920" cy="2598480"/>
+          <a:ext cx="2302560" cy="2598120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3283,9 +3298,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2350800</xdr:colOff>
+      <xdr:colOff>2350440</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>2464920</xdr:rowOff>
+      <xdr:rowOff>2464560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3299,7 +3314,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="24076800"/>
-          <a:ext cx="2350800" cy="2464920"/>
+          <a:ext cx="2350440" cy="2464560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3321,9 +3336,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2140920</xdr:colOff>
+      <xdr:colOff>2140560</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>2464920</xdr:rowOff>
+      <xdr:rowOff>2464560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3337,7 +3352,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="26878320"/>
-          <a:ext cx="2140920" cy="2464920"/>
+          <a:ext cx="2140560" cy="2464560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3359,9 +3374,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112480</xdr:colOff>
+      <xdr:colOff>2112120</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>2455560</xdr:rowOff>
+      <xdr:rowOff>2455200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3375,7 +3390,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="29679840"/>
-          <a:ext cx="2112480" cy="2455560"/>
+          <a:ext cx="2112120" cy="2455200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3397,9 +3412,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112480</xdr:colOff>
+      <xdr:colOff>2112120</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>2522160</xdr:rowOff>
+      <xdr:rowOff>2521800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3413,7 +3428,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="32496120"/>
-          <a:ext cx="2112480" cy="2522160"/>
+          <a:ext cx="2112120" cy="2521800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3435,9 +3450,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1998360</xdr:colOff>
+      <xdr:colOff>1998000</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>2369880</xdr:rowOff>
+      <xdr:rowOff>2369520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3451,7 +3466,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="35517960"/>
-          <a:ext cx="1998360" cy="2369880"/>
+          <a:ext cx="1998000" cy="2369520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3473,9 +3488,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2474640</xdr:colOff>
+      <xdr:colOff>2474280</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>2550600</xdr:rowOff>
+      <xdr:rowOff>2550240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3489,7 +3504,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="38261160"/>
-          <a:ext cx="2474640" cy="2550600"/>
+          <a:ext cx="2474280" cy="2550240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3511,9 +3526,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1941120</xdr:colOff>
+      <xdr:colOff>1940760</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2569680</xdr:rowOff>
+      <xdr:rowOff>2569320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3527,7 +3542,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="41193720"/>
-          <a:ext cx="1941120" cy="2569680"/>
+          <a:ext cx="1940760" cy="2569320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3549,9 +3564,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4662000</xdr:colOff>
+      <xdr:colOff>4661640</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>2762280</xdr:rowOff>
+      <xdr:rowOff>2761920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3565,7 +3580,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="45722520"/>
-          <a:ext cx="4662000" cy="2762280"/>
+          <a:ext cx="4661640" cy="2761920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3587,9 +3602,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3722400</xdr:colOff>
+      <xdr:colOff>3722040</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>1817280</xdr:rowOff>
+      <xdr:rowOff>1816920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3603,7 +3618,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="49140720"/>
-          <a:ext cx="3722400" cy="1817280"/>
+          <a:ext cx="3722040" cy="1816920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3625,9 +3640,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4765680</xdr:colOff>
+      <xdr:colOff>4765320</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>2831400</xdr:rowOff>
+      <xdr:rowOff>2831040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3641,7 +3656,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="51640200"/>
-          <a:ext cx="4765680" cy="2831400"/>
+          <a:ext cx="4765320" cy="2831040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3663,9 +3678,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4708440</xdr:colOff>
+      <xdr:colOff>4708080</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>2797200</xdr:rowOff>
+      <xdr:rowOff>2796840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3679,7 +3694,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="25878960" y="55145880"/>
-          <a:ext cx="4708440" cy="2797200"/>
+          <a:ext cx="4708080" cy="2796840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3811,8 +3826,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="105.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="122.86"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="128.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="5" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="69.56"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5198,8 +5216,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="75.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="101.45"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="81.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="5" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="67.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="174.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5487,8 +5508,11 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="96.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="109.59"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="103.16"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="5" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="68.7"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="184.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7258,7 +7282,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="89.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="115.01"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="96.83"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7809,11 +7835,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="81.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="81.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>844</v>
       </c>
     </row>
